--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\codepresso\renewal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEDE0CA-D704-48C1-AA56-77263D036BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B505BB-DF48-44CA-844C-9E3E7474931A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24789" yWindow="-3086" windowWidth="24892" windowHeight="14915" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cities" sheetId="1" r:id="rId1"/>
@@ -26367,9 +26367,6 @@
   </si>
   <si>
     <t>company-hero-desc</t>
-  </si>
-  <si>
-    <t>비전은 &lt;strong&gt;AI 리터러시의 표준화&lt;/strong&gt;. &lt;br:pc&gt;“AI계의 토익”을 만듭니다.</t>
   </si>
   <si>
     <t>company-statement-title</t>
@@ -30618,12 +30615,161 @@
     <t>시작하기</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비전은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;strong&gt;AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리터러시의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표준화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;/strong&gt;. &lt;br&gt;&lt;strong&gt;AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>토익</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>&lt;/strong&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만듭니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -30725,6 +30871,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63744,25 +63897,25 @@
         <v>7169</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>9656</v>
+        <v>9655</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>7170</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>9655</v>
+        <v>9654</v>
       </c>
       <c r="G1" s="23" t="s">
+        <v>9650</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>9651</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="23" t="s">
         <v>9652</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="J1" s="23" t="s">
         <v>9653</v>
-      </c>
-      <c r="J1" s="23" t="s">
-        <v>9654</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -63857,7 +64010,7 @@
         <v>7190</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>9663</v>
+        <v>9662</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>7191</v>
@@ -64011,7 +64164,7 @@
         <v>7221</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>9659</v>
+        <v>9658</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>7222</v>
@@ -64487,7 +64640,7 @@
         <v>7322</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>9658</v>
+        <v>9657</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>7323</v>
@@ -64697,7 +64850,7 @@
         <v>7366</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>9662</v>
+        <v>9661</v>
       </c>
       <c r="E68" s="22" t="s">
         <v>7367</v>
@@ -64739,7 +64892,7 @@
         <v>7374</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>9666</v>
+        <v>9665</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>7375</v>
@@ -64753,7 +64906,7 @@
         <v>7376</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>9665</v>
+        <v>9664</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>7377</v>
@@ -64767,7 +64920,7 @@
         <v>7378</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>9660</v>
+        <v>9659</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>7379</v>
@@ -64809,7 +64962,7 @@
         <v>7386</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>9661</v>
+        <v>9660</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>7387</v>
@@ -64893,7 +65046,7 @@
         <v>7403</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>9664</v>
+        <v>9663</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>7404</v>
@@ -65131,7 +65284,7 @@
         <v>7452</v>
       </c>
       <c r="C99" s="30" t="s">
-        <v>9657</v>
+        <v>9656</v>
       </c>
       <c r="E99" s="22" t="s">
         <v>7454</v>
@@ -72258,8 +72411,8 @@
       <c r="B705" s="26" t="s">
         <v>8780</v>
       </c>
-      <c r="C705" s="21" t="s">
-        <v>8781</v>
+      <c r="C705" s="31" t="s">
+        <v>9666</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72267,10 +72420,10 @@
         <v>4</v>
       </c>
       <c r="B706" s="26" t="s">
+        <v>8781</v>
+      </c>
+      <c r="C706" s="21" t="s">
         <v>8782</v>
-      </c>
-      <c r="C706" s="21" t="s">
-        <v>8783</v>
       </c>
     </row>
     <row r="707" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72278,10 +72431,10 @@
         <v>4</v>
       </c>
       <c r="B707" s="26" t="s">
+        <v>8783</v>
+      </c>
+      <c r="C707" s="21" t="s">
         <v>8784</v>
-      </c>
-      <c r="C707" s="21" t="s">
-        <v>8785</v>
       </c>
     </row>
     <row r="708" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72289,10 +72442,10 @@
         <v>4</v>
       </c>
       <c r="B708" s="26" t="s">
+        <v>8785</v>
+      </c>
+      <c r="C708" s="21" t="s">
         <v>8786</v>
-      </c>
-      <c r="C708" s="21" t="s">
-        <v>8787</v>
       </c>
     </row>
     <row r="709" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72300,10 +72453,10 @@
         <v>4</v>
       </c>
       <c r="B709" s="26" t="s">
+        <v>8787</v>
+      </c>
+      <c r="C709" s="21" t="s">
         <v>8788</v>
-      </c>
-      <c r="C709" s="21" t="s">
-        <v>8789</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72311,10 +72464,10 @@
         <v>4</v>
       </c>
       <c r="B710" s="26" t="s">
+        <v>8789</v>
+      </c>
+      <c r="C710" s="21" t="s">
         <v>8790</v>
-      </c>
-      <c r="C710" s="21" t="s">
-        <v>8791</v>
       </c>
     </row>
     <row r="711" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72322,10 +72475,10 @@
         <v>4</v>
       </c>
       <c r="B711" s="26" t="s">
+        <v>8791</v>
+      </c>
+      <c r="C711" s="21" t="s">
         <v>8792</v>
-      </c>
-      <c r="C711" s="21" t="s">
-        <v>8793</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72333,10 +72486,10 @@
         <v>4</v>
       </c>
       <c r="B712" s="26" t="s">
+        <v>8793</v>
+      </c>
+      <c r="C712" s="21" t="s">
         <v>8794</v>
-      </c>
-      <c r="C712" s="21" t="s">
-        <v>8795</v>
       </c>
     </row>
     <row r="713" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72344,10 +72497,10 @@
         <v>4</v>
       </c>
       <c r="B713" s="26" t="s">
+        <v>8795</v>
+      </c>
+      <c r="C713" s="21" t="s">
         <v>8796</v>
-      </c>
-      <c r="C713" s="21" t="s">
-        <v>8797</v>
       </c>
     </row>
     <row r="714" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72355,10 +72508,10 @@
         <v>4</v>
       </c>
       <c r="B714" s="26" t="s">
+        <v>8797</v>
+      </c>
+      <c r="C714" s="21" t="s">
         <v>8798</v>
-      </c>
-      <c r="C714" s="21" t="s">
-        <v>8799</v>
       </c>
     </row>
     <row r="715" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72366,10 +72519,10 @@
         <v>4</v>
       </c>
       <c r="B715" s="26" t="s">
+        <v>8799</v>
+      </c>
+      <c r="C715" s="21" t="s">
         <v>8800</v>
-      </c>
-      <c r="C715" s="21" t="s">
-        <v>8801</v>
       </c>
     </row>
     <row r="716" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72377,10 +72530,10 @@
         <v>4</v>
       </c>
       <c r="B716" s="26" t="s">
+        <v>8801</v>
+      </c>
+      <c r="C716" s="21" t="s">
         <v>8802</v>
-      </c>
-      <c r="C716" s="21" t="s">
-        <v>8803</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72388,10 +72541,10 @@
         <v>4</v>
       </c>
       <c r="B717" s="26" t="s">
+        <v>8803</v>
+      </c>
+      <c r="C717" s="21" t="s">
         <v>8804</v>
-      </c>
-      <c r="C717" s="21" t="s">
-        <v>8805</v>
       </c>
     </row>
     <row r="718" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72399,10 +72552,10 @@
         <v>4</v>
       </c>
       <c r="B718" s="26" t="s">
+        <v>8805</v>
+      </c>
+      <c r="C718" s="21" t="s">
         <v>8806</v>
-      </c>
-      <c r="C718" s="21" t="s">
-        <v>8807</v>
       </c>
     </row>
     <row r="719" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72410,10 +72563,10 @@
         <v>4</v>
       </c>
       <c r="B719" s="26" t="s">
+        <v>8807</v>
+      </c>
+      <c r="C719" s="21" t="s">
         <v>8808</v>
-      </c>
-      <c r="C719" s="21" t="s">
-        <v>8809</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72421,10 +72574,10 @@
         <v>4</v>
       </c>
       <c r="B720" s="26" t="s">
+        <v>8809</v>
+      </c>
+      <c r="C720" s="21" t="s">
         <v>8810</v>
-      </c>
-      <c r="C720" s="21" t="s">
-        <v>8811</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72432,10 +72585,10 @@
         <v>4</v>
       </c>
       <c r="B721" s="26" t="s">
+        <v>8811</v>
+      </c>
+      <c r="C721" s="21" t="s">
         <v>8812</v>
-      </c>
-      <c r="C721" s="21" t="s">
-        <v>8813</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72443,10 +72596,10 @@
         <v>4</v>
       </c>
       <c r="B722" s="26" t="s">
+        <v>8813</v>
+      </c>
+      <c r="C722" s="21" t="s">
         <v>8814</v>
-      </c>
-      <c r="C722" s="21" t="s">
-        <v>8815</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72454,10 +72607,10 @@
         <v>4</v>
       </c>
       <c r="B723" s="26" t="s">
+        <v>8815</v>
+      </c>
+      <c r="C723" s="21" t="s">
         <v>8816</v>
-      </c>
-      <c r="C723" s="21" t="s">
-        <v>8817</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72465,10 +72618,10 @@
         <v>4</v>
       </c>
       <c r="B724" s="26" t="s">
+        <v>8817</v>
+      </c>
+      <c r="C724" s="21" t="s">
         <v>8818</v>
-      </c>
-      <c r="C724" s="21" t="s">
-        <v>8819</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72476,10 +72629,10 @@
         <v>4</v>
       </c>
       <c r="B725" s="26" t="s">
+        <v>8819</v>
+      </c>
+      <c r="C725" s="21" t="s">
         <v>8820</v>
-      </c>
-      <c r="C725" s="21" t="s">
-        <v>8821</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72487,10 +72640,10 @@
         <v>4</v>
       </c>
       <c r="B726" s="26" t="s">
+        <v>8821</v>
+      </c>
+      <c r="C726" s="21" t="s">
         <v>8822</v>
-      </c>
-      <c r="C726" s="21" t="s">
-        <v>8823</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72498,10 +72651,10 @@
         <v>4</v>
       </c>
       <c r="B727" s="26" t="s">
+        <v>8823</v>
+      </c>
+      <c r="C727" s="21" t="s">
         <v>8824</v>
-      </c>
-      <c r="C727" s="21" t="s">
-        <v>8825</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72509,10 +72662,10 @@
         <v>4</v>
       </c>
       <c r="B728" s="26" t="s">
+        <v>8825</v>
+      </c>
+      <c r="C728" s="21" t="s">
         <v>8826</v>
-      </c>
-      <c r="C728" s="21" t="s">
-        <v>8827</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72520,10 +72673,10 @@
         <v>4</v>
       </c>
       <c r="B729" s="26" t="s">
+        <v>8827</v>
+      </c>
+      <c r="C729" s="21" t="s">
         <v>8828</v>
-      </c>
-      <c r="C729" s="21" t="s">
-        <v>8829</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72531,10 +72684,10 @@
         <v>4</v>
       </c>
       <c r="B730" s="26" t="s">
+        <v>8829</v>
+      </c>
+      <c r="C730" s="21" t="s">
         <v>8830</v>
-      </c>
-      <c r="C730" s="21" t="s">
-        <v>8831</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72542,10 +72695,10 @@
         <v>4</v>
       </c>
       <c r="B731" s="26" t="s">
+        <v>8831</v>
+      </c>
+      <c r="C731" s="21" t="s">
         <v>8832</v>
-      </c>
-      <c r="C731" s="21" t="s">
-        <v>8833</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72553,10 +72706,10 @@
         <v>4</v>
       </c>
       <c r="B732" s="26" t="s">
+        <v>8833</v>
+      </c>
+      <c r="C732" s="21" t="s">
         <v>8834</v>
-      </c>
-      <c r="C732" s="21" t="s">
-        <v>8835</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72564,10 +72717,10 @@
         <v>4</v>
       </c>
       <c r="B733" s="26" t="s">
+        <v>8835</v>
+      </c>
+      <c r="C733" s="21" t="s">
         <v>8836</v>
-      </c>
-      <c r="C733" s="21" t="s">
-        <v>8837</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72575,10 +72728,10 @@
         <v>4</v>
       </c>
       <c r="B734" s="26" t="s">
+        <v>8837</v>
+      </c>
+      <c r="C734" s="21" t="s">
         <v>8838</v>
-      </c>
-      <c r="C734" s="21" t="s">
-        <v>8839</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72586,10 +72739,10 @@
         <v>4</v>
       </c>
       <c r="B735" s="26" t="s">
+        <v>8839</v>
+      </c>
+      <c r="C735" s="21" t="s">
         <v>8840</v>
-      </c>
-      <c r="C735" s="21" t="s">
-        <v>8841</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72597,10 +72750,10 @@
         <v>4</v>
       </c>
       <c r="B736" s="26" t="s">
+        <v>8841</v>
+      </c>
+      <c r="C736" s="21" t="s">
         <v>8842</v>
-      </c>
-      <c r="C736" s="21" t="s">
-        <v>8843</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72608,10 +72761,10 @@
         <v>4</v>
       </c>
       <c r="B737" s="26" t="s">
+        <v>8843</v>
+      </c>
+      <c r="C737" s="21" t="s">
         <v>8844</v>
-      </c>
-      <c r="C737" s="21" t="s">
-        <v>8845</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72619,10 +72772,10 @@
         <v>4</v>
       </c>
       <c r="B738" s="26" t="s">
+        <v>8845</v>
+      </c>
+      <c r="C738" s="21" t="s">
         <v>8846</v>
-      </c>
-      <c r="C738" s="21" t="s">
-        <v>8847</v>
       </c>
     </row>
     <row r="739" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72630,10 +72783,10 @@
         <v>4</v>
       </c>
       <c r="B739" s="26" t="s">
+        <v>8847</v>
+      </c>
+      <c r="C739" s="21" t="s">
         <v>8848</v>
-      </c>
-      <c r="C739" s="21" t="s">
-        <v>8849</v>
       </c>
     </row>
     <row r="740" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72641,10 +72794,10 @@
         <v>4</v>
       </c>
       <c r="B740" s="26" t="s">
+        <v>8849</v>
+      </c>
+      <c r="C740" s="21" t="s">
         <v>8850</v>
-      </c>
-      <c r="C740" s="21" t="s">
-        <v>8851</v>
       </c>
     </row>
     <row r="741" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72652,10 +72805,10 @@
         <v>4</v>
       </c>
       <c r="B741" s="26" t="s">
+        <v>8851</v>
+      </c>
+      <c r="C741" s="21" t="s">
         <v>8852</v>
-      </c>
-      <c r="C741" s="21" t="s">
-        <v>8853</v>
       </c>
     </row>
     <row r="742" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72663,10 +72816,10 @@
         <v>4</v>
       </c>
       <c r="B742" s="26" t="s">
+        <v>8853</v>
+      </c>
+      <c r="C742" s="21" t="s">
         <v>8854</v>
-      </c>
-      <c r="C742" s="21" t="s">
-        <v>8855</v>
       </c>
     </row>
     <row r="743" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72674,10 +72827,10 @@
         <v>4</v>
       </c>
       <c r="B743" s="26" t="s">
+        <v>8855</v>
+      </c>
+      <c r="C743" s="21" t="s">
         <v>8856</v>
-      </c>
-      <c r="C743" s="21" t="s">
-        <v>8857</v>
       </c>
     </row>
     <row r="744" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72685,10 +72838,10 @@
         <v>4</v>
       </c>
       <c r="B744" s="26" t="s">
+        <v>8857</v>
+      </c>
+      <c r="C744" s="21" t="s">
         <v>8858</v>
-      </c>
-      <c r="C744" s="21" t="s">
-        <v>8859</v>
       </c>
     </row>
     <row r="745" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72696,10 +72849,10 @@
         <v>4</v>
       </c>
       <c r="B745" s="26" t="s">
+        <v>8859</v>
+      </c>
+      <c r="C745" s="21" t="s">
         <v>8860</v>
-      </c>
-      <c r="C745" s="21" t="s">
-        <v>8861</v>
       </c>
     </row>
     <row r="746" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72707,10 +72860,10 @@
         <v>4</v>
       </c>
       <c r="B746" s="26" t="s">
+        <v>8861</v>
+      </c>
+      <c r="C746" s="21" t="s">
         <v>8862</v>
-      </c>
-      <c r="C746" s="21" t="s">
-        <v>8863</v>
       </c>
     </row>
     <row r="747" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72718,10 +72871,10 @@
         <v>4</v>
       </c>
       <c r="B747" s="26" t="s">
+        <v>8863</v>
+      </c>
+      <c r="C747" s="21" t="s">
         <v>8864</v>
-      </c>
-      <c r="C747" s="21" t="s">
-        <v>8865</v>
       </c>
     </row>
     <row r="748" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72729,10 +72882,10 @@
         <v>4</v>
       </c>
       <c r="B748" s="26" t="s">
+        <v>8865</v>
+      </c>
+      <c r="C748" s="21" t="s">
         <v>8866</v>
-      </c>
-      <c r="C748" s="21" t="s">
-        <v>8867</v>
       </c>
     </row>
     <row r="749" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72740,10 +72893,10 @@
         <v>4</v>
       </c>
       <c r="B749" s="26" t="s">
+        <v>8867</v>
+      </c>
+      <c r="C749" s="21" t="s">
         <v>8868</v>
-      </c>
-      <c r="C749" s="21" t="s">
-        <v>8869</v>
       </c>
     </row>
     <row r="750" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72751,10 +72904,10 @@
         <v>4</v>
       </c>
       <c r="B750" s="26" t="s">
+        <v>8869</v>
+      </c>
+      <c r="C750" s="21" t="s">
         <v>8870</v>
-      </c>
-      <c r="C750" s="21" t="s">
-        <v>8871</v>
       </c>
     </row>
     <row r="751" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72762,10 +72915,10 @@
         <v>4</v>
       </c>
       <c r="B751" s="26" t="s">
+        <v>8871</v>
+      </c>
+      <c r="C751" s="21" t="s">
         <v>8872</v>
-      </c>
-      <c r="C751" s="21" t="s">
-        <v>8873</v>
       </c>
     </row>
     <row r="752" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72773,10 +72926,10 @@
         <v>4</v>
       </c>
       <c r="B752" s="26" t="s">
+        <v>8873</v>
+      </c>
+      <c r="C752" s="21" t="s">
         <v>8874</v>
-      </c>
-      <c r="C752" s="21" t="s">
-        <v>8875</v>
       </c>
     </row>
     <row r="753" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -72784,392 +72937,392 @@
         <v>4</v>
       </c>
       <c r="B753" s="26" t="s">
+        <v>8875</v>
+      </c>
+      <c r="C753" s="21" t="s">
         <v>8876</v>
-      </c>
-      <c r="C753" s="21" t="s">
-        <v>8877</v>
       </c>
     </row>
     <row r="754" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="28" t="s">
+        <v>8877</v>
+      </c>
+      <c r="B754" s="26" t="s">
         <v>8878</v>
       </c>
-      <c r="B754" s="26" t="s">
+      <c r="C754" s="21" t="s">
         <v>8879</v>
-      </c>
-      <c r="C754" s="21" t="s">
-        <v>8880</v>
       </c>
     </row>
     <row r="755" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B755" s="26" t="s">
+        <v>8880</v>
+      </c>
+      <c r="C755" s="21" t="s">
         <v>8881</v>
-      </c>
-      <c r="C755" s="21" t="s">
-        <v>8882</v>
       </c>
     </row>
     <row r="756" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B756" s="26" t="s">
+        <v>8882</v>
+      </c>
+      <c r="C756" s="21" t="s">
         <v>8883</v>
-      </c>
-      <c r="C756" s="21" t="s">
-        <v>8884</v>
       </c>
     </row>
     <row r="757" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B757" s="26" t="s">
+        <v>8884</v>
+      </c>
+      <c r="C757" s="21" t="s">
         <v>8885</v>
-      </c>
-      <c r="C757" s="21" t="s">
-        <v>8886</v>
       </c>
     </row>
     <row r="758" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B758" s="26" t="s">
+        <v>8886</v>
+      </c>
+      <c r="C758" s="21" t="s">
         <v>8887</v>
-      </c>
-      <c r="C758" s="21" t="s">
-        <v>8888</v>
       </c>
     </row>
     <row r="759" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B759" s="26" t="s">
+        <v>8888</v>
+      </c>
+      <c r="C759" s="21" t="s">
         <v>8889</v>
-      </c>
-      <c r="C759" s="21" t="s">
-        <v>8890</v>
       </c>
     </row>
     <row r="760" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B760" s="26" t="s">
+        <v>8890</v>
+      </c>
+      <c r="C760" s="21" t="s">
         <v>8891</v>
-      </c>
-      <c r="C760" s="21" t="s">
-        <v>8892</v>
       </c>
     </row>
     <row r="761" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B761" s="26" t="s">
+        <v>8892</v>
+      </c>
+      <c r="C761" s="21" t="s">
         <v>8893</v>
-      </c>
-      <c r="C761" s="21" t="s">
-        <v>8894</v>
       </c>
     </row>
     <row r="762" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B762" s="26" t="s">
+        <v>8894</v>
+      </c>
+      <c r="C762" s="21" t="s">
         <v>8895</v>
-      </c>
-      <c r="C762" s="21" t="s">
-        <v>8896</v>
       </c>
     </row>
     <row r="763" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B763" s="26" t="s">
+        <v>8896</v>
+      </c>
+      <c r="C763" s="21" t="s">
         <v>8897</v>
-      </c>
-      <c r="C763" s="21" t="s">
-        <v>8898</v>
       </c>
     </row>
     <row r="764" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B764" s="26" t="s">
+        <v>8898</v>
+      </c>
+      <c r="C764" s="21" t="s">
         <v>8899</v>
-      </c>
-      <c r="C764" s="21" t="s">
-        <v>8900</v>
       </c>
     </row>
     <row r="765" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B765" s="26" t="s">
+        <v>8900</v>
+      </c>
+      <c r="C765" s="21" t="s">
         <v>8901</v>
-      </c>
-      <c r="C765" s="21" t="s">
-        <v>8902</v>
       </c>
     </row>
     <row r="766" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B766" s="26" t="s">
+        <v>8902</v>
+      </c>
+      <c r="C766" s="21" t="s">
         <v>8903</v>
-      </c>
-      <c r="C766" s="21" t="s">
-        <v>8904</v>
       </c>
     </row>
     <row r="767" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B767" s="26" t="s">
+        <v>8904</v>
+      </c>
+      <c r="C767" s="21" t="s">
         <v>8905</v>
-      </c>
-      <c r="C767" s="21" t="s">
-        <v>8906</v>
       </c>
     </row>
     <row r="768" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B768" s="26" t="s">
+        <v>8906</v>
+      </c>
+      <c r="C768" s="21" t="s">
         <v>8907</v>
-      </c>
-      <c r="C768" s="21" t="s">
-        <v>8908</v>
       </c>
     </row>
     <row r="769" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B769" s="26" t="s">
+        <v>8908</v>
+      </c>
+      <c r="C769" s="21" t="s">
         <v>8909</v>
-      </c>
-      <c r="C769" s="21" t="s">
-        <v>8910</v>
       </c>
     </row>
     <row r="770" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B770" s="26" t="s">
+        <v>8910</v>
+      </c>
+      <c r="C770" s="21" t="s">
         <v>8911</v>
-      </c>
-      <c r="C770" s="21" t="s">
-        <v>8912</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B771" s="26" t="s">
+        <v>8912</v>
+      </c>
+      <c r="C771" s="21" t="s">
         <v>8913</v>
-      </c>
-      <c r="C771" s="21" t="s">
-        <v>8914</v>
       </c>
     </row>
     <row r="772" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B772" s="26" t="s">
+        <v>8914</v>
+      </c>
+      <c r="C772" s="21" t="s">
         <v>8915</v>
-      </c>
-      <c r="C772" s="21" t="s">
-        <v>8916</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B773" s="26" t="s">
+        <v>8916</v>
+      </c>
+      <c r="C773" s="21" t="s">
         <v>8917</v>
-      </c>
-      <c r="C773" s="21" t="s">
-        <v>8918</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B774" s="26" t="s">
+        <v>8918</v>
+      </c>
+      <c r="C774" s="21" t="s">
         <v>8919</v>
-      </c>
-      <c r="C774" s="21" t="s">
-        <v>8920</v>
       </c>
     </row>
     <row r="775" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B775" s="26" t="s">
+        <v>8920</v>
+      </c>
+      <c r="C775" s="21" t="s">
         <v>8921</v>
-      </c>
-      <c r="C775" s="21" t="s">
-        <v>8922</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B776" s="26" t="s">
-        <v>8923</v>
+        <v>8922</v>
       </c>
       <c r="C776" s="21" t="s">
-        <v>8888</v>
+        <v>8887</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B777" s="26" t="s">
+        <v>8923</v>
+      </c>
+      <c r="C777" s="21" t="s">
         <v>8924</v>
-      </c>
-      <c r="C777" s="21" t="s">
-        <v>8925</v>
       </c>
     </row>
     <row r="778" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B778" s="26" t="s">
+        <v>8925</v>
+      </c>
+      <c r="C778" s="21" t="s">
         <v>8926</v>
-      </c>
-      <c r="C778" s="21" t="s">
-        <v>8927</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B779" s="26" t="s">
+        <v>8927</v>
+      </c>
+      <c r="C779" s="21" t="s">
         <v>8928</v>
-      </c>
-      <c r="C779" s="21" t="s">
-        <v>8929</v>
       </c>
     </row>
     <row r="780" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B780" s="26" t="s">
-        <v>8930</v>
+        <v>8929</v>
       </c>
       <c r="C780" s="21" t="s">
-        <v>8890</v>
+        <v>8889</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B781" s="26" t="s">
+        <v>8930</v>
+      </c>
+      <c r="C781" s="21" t="s">
         <v>8931</v>
-      </c>
-      <c r="C781" s="21" t="s">
-        <v>8932</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B782" s="26" t="s">
+        <v>8932</v>
+      </c>
+      <c r="C782" s="21" t="s">
         <v>8933</v>
-      </c>
-      <c r="C782" s="21" t="s">
-        <v>8934</v>
       </c>
     </row>
     <row r="783" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B783" s="26" t="s">
+        <v>8934</v>
+      </c>
+      <c r="C783" s="21" t="s">
         <v>8935</v>
-      </c>
-      <c r="C783" s="21" t="s">
-        <v>8936</v>
       </c>
     </row>
     <row r="784" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B784" s="26" t="s">
-        <v>8937</v>
+        <v>8936</v>
       </c>
       <c r="C784" s="21" t="s">
-        <v>8892</v>
+        <v>8891</v>
       </c>
     </row>
     <row r="785" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B785" s="26" t="s">
+        <v>8937</v>
+      </c>
+      <c r="C785" s="21" t="s">
         <v>8938</v>
-      </c>
-      <c r="C785" s="21" t="s">
-        <v>8939</v>
       </c>
     </row>
     <row r="786" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B786" s="26" t="s">
+        <v>8939</v>
+      </c>
+      <c r="C786" s="21" t="s">
         <v>8940</v>
-      </c>
-      <c r="C786" s="21" t="s">
-        <v>8941</v>
       </c>
     </row>
     <row r="787" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B787" s="26" t="s">
+        <v>8941</v>
+      </c>
+      <c r="C787" s="21" t="s">
         <v>8942</v>
-      </c>
-      <c r="C787" s="21" t="s">
-        <v>8943</v>
       </c>
     </row>
     <row r="788" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B788" s="26" t="s">
-        <v>8944</v>
+        <v>8943</v>
       </c>
       <c r="C788" s="21" t="s">
         <v>7999</v>
@@ -73177,153 +73330,153 @@
     </row>
     <row r="789" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B789" s="26" t="s">
+        <v>8944</v>
+      </c>
+      <c r="C789" s="21" t="s">
         <v>8945</v>
-      </c>
-      <c r="C789" s="21" t="s">
-        <v>8946</v>
       </c>
     </row>
     <row r="790" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B790" s="26" t="s">
+        <v>8946</v>
+      </c>
+      <c r="C790" s="21" t="s">
         <v>8947</v>
-      </c>
-      <c r="C790" s="21" t="s">
-        <v>8948</v>
       </c>
     </row>
     <row r="791" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B791" s="26" t="s">
+        <v>8948</v>
+      </c>
+      <c r="C791" s="21" t="s">
         <v>8949</v>
-      </c>
-      <c r="C791" s="21" t="s">
-        <v>8950</v>
       </c>
     </row>
     <row r="792" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B792" s="26" t="s">
+        <v>8950</v>
+      </c>
+      <c r="C792" s="21" t="s">
         <v>8951</v>
-      </c>
-      <c r="C792" s="21" t="s">
-        <v>8952</v>
       </c>
     </row>
     <row r="793" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B793" s="26" t="s">
+        <v>8952</v>
+      </c>
+      <c r="C793" s="21" t="s">
         <v>8953</v>
-      </c>
-      <c r="C793" s="21" t="s">
-        <v>8954</v>
       </c>
     </row>
     <row r="794" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B794" s="26" t="s">
+        <v>8954</v>
+      </c>
+      <c r="C794" s="21" t="s">
         <v>8955</v>
-      </c>
-      <c r="C794" s="21" t="s">
-        <v>8956</v>
       </c>
     </row>
     <row r="795" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B795" s="26" t="s">
+        <v>8956</v>
+      </c>
+      <c r="C795" s="21" t="s">
         <v>8957</v>
-      </c>
-      <c r="C795" s="21" t="s">
-        <v>8958</v>
       </c>
     </row>
     <row r="796" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B796" s="26" t="s">
+        <v>8958</v>
+      </c>
+      <c r="C796" s="21" t="s">
         <v>8959</v>
-      </c>
-      <c r="C796" s="21" t="s">
-        <v>8960</v>
       </c>
     </row>
     <row r="797" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B797" s="26" t="s">
+        <v>8960</v>
+      </c>
+      <c r="C797" s="21" t="s">
         <v>8961</v>
-      </c>
-      <c r="C797" s="21" t="s">
-        <v>8962</v>
       </c>
     </row>
     <row r="798" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B798" s="26" t="s">
+        <v>8962</v>
+      </c>
+      <c r="C798" s="21" t="s">
         <v>8963</v>
-      </c>
-      <c r="C798" s="21" t="s">
-        <v>8964</v>
       </c>
     </row>
     <row r="799" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B799" s="26" t="s">
+        <v>8964</v>
+      </c>
+      <c r="C799" s="21" t="s">
         <v>8965</v>
-      </c>
-      <c r="C799" s="21" t="s">
-        <v>8966</v>
       </c>
     </row>
     <row r="800" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B800" s="26" t="s">
+        <v>8966</v>
+      </c>
+      <c r="C800" s="21" t="s">
         <v>8967</v>
-      </c>
-      <c r="C800" s="21" t="s">
-        <v>8968</v>
       </c>
     </row>
     <row r="801" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B801" s="26" t="s">
+        <v>8968</v>
+      </c>
+      <c r="C801" s="21" t="s">
         <v>8969</v>
-      </c>
-      <c r="C801" s="21" t="s">
-        <v>8970</v>
       </c>
     </row>
     <row r="802" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B802" s="26" t="s">
-        <v>8971</v>
+        <v>8970</v>
       </c>
       <c r="C802" s="21" t="s">
         <v>7480</v>
@@ -73331,43 +73484,43 @@
     </row>
     <row r="803" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B803" s="26" t="s">
-        <v>8972</v>
+        <v>8971</v>
       </c>
       <c r="C803" s="21" t="s">
-        <v>8886</v>
+        <v>8885</v>
       </c>
     </row>
     <row r="804" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B804" s="26" t="s">
+        <v>8972</v>
+      </c>
+      <c r="C804" s="21" t="s">
         <v>8973</v>
-      </c>
-      <c r="C804" s="21" t="s">
-        <v>8974</v>
       </c>
     </row>
     <row r="805" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B805" s="26" t="s">
+        <v>8974</v>
+      </c>
+      <c r="C805" s="21" t="s">
         <v>8975</v>
-      </c>
-      <c r="C805" s="21" t="s">
-        <v>8976</v>
       </c>
     </row>
     <row r="806" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B806" s="26" t="s">
-        <v>8977</v>
+        <v>8976</v>
       </c>
       <c r="C806" s="21" t="s">
         <v>7812</v>
@@ -73375,120 +73528,120 @@
     </row>
     <row r="807" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B807" s="26" t="s">
+        <v>8977</v>
+      </c>
+      <c r="C807" s="21" t="s">
         <v>8978</v>
-      </c>
-      <c r="C807" s="21" t="s">
-        <v>8979</v>
       </c>
     </row>
     <row r="808" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B808" s="26" t="s">
+        <v>8979</v>
+      </c>
+      <c r="C808" s="21" t="s">
         <v>8980</v>
-      </c>
-      <c r="C808" s="21" t="s">
-        <v>8981</v>
       </c>
     </row>
     <row r="809" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B809" s="26" t="s">
+        <v>8981</v>
+      </c>
+      <c r="C809" s="21" t="s">
         <v>8982</v>
-      </c>
-      <c r="C809" s="21" t="s">
-        <v>8983</v>
       </c>
     </row>
     <row r="810" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B810" s="26" t="s">
+        <v>8983</v>
+      </c>
+      <c r="C810" s="21" t="s">
         <v>8984</v>
-      </c>
-      <c r="C810" s="21" t="s">
-        <v>8985</v>
       </c>
     </row>
     <row r="811" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B811" s="26" t="s">
+        <v>8985</v>
+      </c>
+      <c r="C811" s="21" t="s">
         <v>8986</v>
-      </c>
-      <c r="C811" s="21" t="s">
-        <v>8987</v>
       </c>
     </row>
     <row r="812" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B812" s="26" t="s">
+        <v>8987</v>
+      </c>
+      <c r="C812" s="21" t="s">
         <v>8988</v>
-      </c>
-      <c r="C812" s="21" t="s">
-        <v>8989</v>
       </c>
     </row>
     <row r="813" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B813" s="26" t="s">
+        <v>8989</v>
+      </c>
+      <c r="C813" s="21" t="s">
         <v>8990</v>
-      </c>
-      <c r="C813" s="21" t="s">
-        <v>8991</v>
       </c>
     </row>
     <row r="814" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B814" s="26" t="s">
+        <v>8991</v>
+      </c>
+      <c r="C814" s="21" t="s">
         <v>8992</v>
-      </c>
-      <c r="C814" s="21" t="s">
-        <v>8993</v>
       </c>
     </row>
     <row r="815" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B815" s="26" t="s">
+        <v>8993</v>
+      </c>
+      <c r="C815" s="21" t="s">
         <v>8994</v>
-      </c>
-      <c r="C815" s="21" t="s">
-        <v>8995</v>
       </c>
     </row>
     <row r="816" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B816" s="26" t="s">
+        <v>8995</v>
+      </c>
+      <c r="C816" s="21" t="s">
         <v>8996</v>
-      </c>
-      <c r="C816" s="21" t="s">
-        <v>8997</v>
       </c>
     </row>
     <row r="817" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B817" s="26" t="s">
-        <v>8998</v>
+        <v>8997</v>
       </c>
       <c r="C817" s="21" t="s">
         <v>7762</v>
@@ -73496,54 +73649,54 @@
     </row>
     <row r="818" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B818" s="26" t="s">
+        <v>8998</v>
+      </c>
+      <c r="C818" s="21" t="s">
         <v>8999</v>
-      </c>
-      <c r="C818" s="21" t="s">
-        <v>9000</v>
       </c>
     </row>
     <row r="819" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B819" s="26" t="s">
+        <v>9000</v>
+      </c>
+      <c r="C819" s="21" t="s">
         <v>9001</v>
-      </c>
-      <c r="C819" s="21" t="s">
-        <v>9002</v>
       </c>
     </row>
     <row r="820" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B820" s="26" t="s">
+        <v>9002</v>
+      </c>
+      <c r="C820" s="21" t="s">
         <v>9003</v>
-      </c>
-      <c r="C820" s="21" t="s">
-        <v>9004</v>
       </c>
     </row>
     <row r="821" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B821" s="26" t="s">
+        <v>9004</v>
+      </c>
+      <c r="C821" s="21" t="s">
         <v>9005</v>
-      </c>
-      <c r="C821" s="21" t="s">
-        <v>9006</v>
       </c>
     </row>
     <row r="822" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B822" s="26" t="s">
-        <v>9007</v>
+        <v>9006</v>
       </c>
       <c r="C822" s="21" t="s">
         <v>7759</v>
@@ -73551,670 +73704,670 @@
     </row>
     <row r="823" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B823" s="26" t="s">
+        <v>9007</v>
+      </c>
+      <c r="C823" s="21" t="s">
         <v>9008</v>
-      </c>
-      <c r="C823" s="21" t="s">
-        <v>9009</v>
       </c>
     </row>
     <row r="824" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B824" s="26" t="s">
+        <v>9009</v>
+      </c>
+      <c r="C824" s="21" t="s">
         <v>9010</v>
-      </c>
-      <c r="C824" s="21" t="s">
-        <v>9011</v>
       </c>
     </row>
     <row r="825" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B825" s="26" t="s">
+        <v>9011</v>
+      </c>
+      <c r="C825" s="21" t="s">
         <v>9012</v>
-      </c>
-      <c r="C825" s="21" t="s">
-        <v>9013</v>
       </c>
     </row>
     <row r="826" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B826" s="26" t="s">
+        <v>9013</v>
+      </c>
+      <c r="C826" s="21" t="s">
         <v>9014</v>
-      </c>
-      <c r="C826" s="21" t="s">
-        <v>9015</v>
       </c>
     </row>
     <row r="827" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B827" s="26" t="s">
+        <v>9015</v>
+      </c>
+      <c r="C827" s="21" t="s">
         <v>9016</v>
-      </c>
-      <c r="C827" s="21" t="s">
-        <v>9017</v>
       </c>
     </row>
     <row r="828" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B828" s="26" t="s">
+        <v>9017</v>
+      </c>
+      <c r="C828" s="21" t="s">
         <v>9018</v>
-      </c>
-      <c r="C828" s="21" t="s">
-        <v>9019</v>
       </c>
     </row>
     <row r="829" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B829" s="26" t="s">
+        <v>9019</v>
+      </c>
+      <c r="C829" s="21" t="s">
         <v>9020</v>
-      </c>
-      <c r="C829" s="21" t="s">
-        <v>9021</v>
       </c>
     </row>
     <row r="830" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="28" t="s">
-        <v>8878</v>
+        <v>8877</v>
       </c>
       <c r="B830" s="26" t="s">
+        <v>9021</v>
+      </c>
+      <c r="C830" s="21" t="s">
         <v>9022</v>
-      </c>
-      <c r="C830" s="21" t="s">
-        <v>9023</v>
       </c>
     </row>
     <row r="831" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="28" t="s">
+        <v>9023</v>
+      </c>
+      <c r="B831" s="26" t="s">
         <v>9024</v>
       </c>
-      <c r="B831" s="26" t="s">
+      <c r="C831" s="21" t="s">
         <v>9025</v>
-      </c>
-      <c r="C831" s="21" t="s">
-        <v>9026</v>
       </c>
     </row>
     <row r="832" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B832" s="26" t="s">
+        <v>9026</v>
+      </c>
+      <c r="C832" s="21" t="s">
         <v>9027</v>
-      </c>
-      <c r="C832" s="21" t="s">
-        <v>9028</v>
       </c>
     </row>
     <row r="833" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B833" s="26" t="s">
+        <v>9028</v>
+      </c>
+      <c r="C833" s="21" t="s">
         <v>9029</v>
-      </c>
-      <c r="C833" s="21" t="s">
-        <v>9030</v>
       </c>
     </row>
     <row r="834" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B834" s="26" t="s">
+        <v>9030</v>
+      </c>
+      <c r="C834" s="21" t="s">
         <v>9031</v>
-      </c>
-      <c r="C834" s="21" t="s">
-        <v>9032</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B835" s="26" t="s">
+        <v>9032</v>
+      </c>
+      <c r="C835" s="21" t="s">
         <v>9033</v>
-      </c>
-      <c r="C835" s="21" t="s">
-        <v>9034</v>
       </c>
     </row>
     <row r="836" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B836" s="26" t="s">
+        <v>9034</v>
+      </c>
+      <c r="C836" s="21" t="s">
         <v>9035</v>
-      </c>
-      <c r="C836" s="21" t="s">
-        <v>9036</v>
       </c>
     </row>
     <row r="837" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B837" s="26" t="s">
+        <v>9036</v>
+      </c>
+      <c r="C837" s="21" t="s">
         <v>9037</v>
-      </c>
-      <c r="C837" s="21" t="s">
-        <v>9038</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B838" s="26" t="s">
+        <v>9038</v>
+      </c>
+      <c r="C838" s="21" t="s">
         <v>9039</v>
-      </c>
-      <c r="C838" s="21" t="s">
-        <v>9040</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B839" s="26" t="s">
+        <v>9040</v>
+      </c>
+      <c r="C839" s="21" t="s">
         <v>9041</v>
-      </c>
-      <c r="C839" s="21" t="s">
-        <v>9042</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B840" s="26" t="s">
+        <v>9042</v>
+      </c>
+      <c r="C840" s="21" t="s">
         <v>9043</v>
-      </c>
-      <c r="C840" s="21" t="s">
-        <v>9044</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B841" s="26" t="s">
+        <v>9044</v>
+      </c>
+      <c r="C841" s="21" t="s">
         <v>9045</v>
-      </c>
-      <c r="C841" s="21" t="s">
-        <v>9046</v>
       </c>
     </row>
     <row r="842" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B842" s="26" t="s">
+        <v>9046</v>
+      </c>
+      <c r="C842" s="21" t="s">
         <v>9047</v>
-      </c>
-      <c r="C842" s="21" t="s">
-        <v>9048</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B843" s="26" t="s">
+        <v>9048</v>
+      </c>
+      <c r="C843" s="21" t="s">
         <v>9049</v>
-      </c>
-      <c r="C843" s="21" t="s">
-        <v>9050</v>
       </c>
     </row>
     <row r="844" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B844" s="26" t="s">
+        <v>9050</v>
+      </c>
+      <c r="C844" s="21" t="s">
         <v>9051</v>
-      </c>
-      <c r="C844" s="21" t="s">
-        <v>9052</v>
       </c>
     </row>
     <row r="845" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B845" s="26" t="s">
+        <v>9052</v>
+      </c>
+      <c r="C845" s="21" t="s">
         <v>9053</v>
-      </c>
-      <c r="C845" s="21" t="s">
-        <v>9054</v>
       </c>
     </row>
     <row r="846" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B846" s="26" t="s">
+        <v>9054</v>
+      </c>
+      <c r="C846" s="21" t="s">
         <v>9055</v>
-      </c>
-      <c r="C846" s="21" t="s">
-        <v>9056</v>
       </c>
     </row>
     <row r="847" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B847" s="26" t="s">
+        <v>9056</v>
+      </c>
+      <c r="C847" s="21" t="s">
         <v>9057</v>
-      </c>
-      <c r="C847" s="21" t="s">
-        <v>9058</v>
       </c>
     </row>
     <row r="848" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B848" s="26" t="s">
+        <v>9058</v>
+      </c>
+      <c r="C848" s="21" t="s">
         <v>9059</v>
-      </c>
-      <c r="C848" s="21" t="s">
-        <v>9060</v>
       </c>
     </row>
     <row r="849" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B849" s="26" t="s">
+        <v>9060</v>
+      </c>
+      <c r="C849" s="21" t="s">
         <v>9061</v>
-      </c>
-      <c r="C849" s="21" t="s">
-        <v>9062</v>
       </c>
     </row>
     <row r="850" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B850" s="26" t="s">
+        <v>9062</v>
+      </c>
+      <c r="C850" s="21" t="s">
         <v>9063</v>
-      </c>
-      <c r="C850" s="21" t="s">
-        <v>9064</v>
       </c>
     </row>
     <row r="851" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B851" s="26" t="s">
+        <v>9064</v>
+      </c>
+      <c r="C851" s="21" t="s">
         <v>9065</v>
-      </c>
-      <c r="C851" s="21" t="s">
-        <v>9066</v>
       </c>
     </row>
     <row r="852" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B852" s="26" t="s">
+        <v>9066</v>
+      </c>
+      <c r="C852" s="21" t="s">
         <v>9067</v>
-      </c>
-      <c r="C852" s="21" t="s">
-        <v>9068</v>
       </c>
     </row>
     <row r="853" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B853" s="26" t="s">
+        <v>9068</v>
+      </c>
+      <c r="C853" s="21" t="s">
         <v>9069</v>
-      </c>
-      <c r="C853" s="21" t="s">
-        <v>9070</v>
       </c>
     </row>
     <row r="854" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B854" s="26" t="s">
+        <v>9070</v>
+      </c>
+      <c r="C854" s="21" t="s">
         <v>9071</v>
-      </c>
-      <c r="C854" s="21" t="s">
-        <v>9072</v>
       </c>
     </row>
     <row r="855" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B855" s="26" t="s">
+        <v>9072</v>
+      </c>
+      <c r="C855" s="21" t="s">
         <v>9073</v>
-      </c>
-      <c r="C855" s="21" t="s">
-        <v>9074</v>
       </c>
     </row>
     <row r="856" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B856" s="26" t="s">
+        <v>9074</v>
+      </c>
+      <c r="C856" s="21" t="s">
         <v>9075</v>
-      </c>
-      <c r="C856" s="21" t="s">
-        <v>9076</v>
       </c>
     </row>
     <row r="857" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B857" s="26" t="s">
+        <v>9076</v>
+      </c>
+      <c r="C857" s="21" t="s">
         <v>9077</v>
-      </c>
-      <c r="C857" s="21" t="s">
-        <v>9078</v>
       </c>
     </row>
     <row r="858" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B858" s="26" t="s">
+        <v>9078</v>
+      </c>
+      <c r="C858" s="21" t="s">
         <v>9079</v>
-      </c>
-      <c r="C858" s="21" t="s">
-        <v>9080</v>
       </c>
     </row>
     <row r="859" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B859" s="26" t="s">
+        <v>9080</v>
+      </c>
+      <c r="C859" s="21" t="s">
         <v>9081</v>
-      </c>
-      <c r="C859" s="21" t="s">
-        <v>9082</v>
       </c>
     </row>
     <row r="860" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B860" s="26" t="s">
+        <v>9082</v>
+      </c>
+      <c r="C860" s="21" t="s">
         <v>9083</v>
-      </c>
-      <c r="C860" s="21" t="s">
-        <v>9084</v>
       </c>
     </row>
     <row r="861" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B861" s="26" t="s">
+        <v>9084</v>
+      </c>
+      <c r="C861" s="21" t="s">
         <v>9085</v>
-      </c>
-      <c r="C861" s="21" t="s">
-        <v>9086</v>
       </c>
     </row>
     <row r="862" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B862" s="26" t="s">
+        <v>9086</v>
+      </c>
+      <c r="C862" s="21" t="s">
         <v>9087</v>
-      </c>
-      <c r="C862" s="21" t="s">
-        <v>9088</v>
       </c>
     </row>
     <row r="863" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B863" s="26" t="s">
+        <v>9088</v>
+      </c>
+      <c r="C863" s="21" t="s">
         <v>9089</v>
-      </c>
-      <c r="C863" s="21" t="s">
-        <v>9090</v>
       </c>
     </row>
     <row r="864" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B864" s="26" t="s">
+        <v>9090</v>
+      </c>
+      <c r="C864" s="21" t="s">
         <v>9091</v>
-      </c>
-      <c r="C864" s="21" t="s">
-        <v>9092</v>
       </c>
     </row>
     <row r="865" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B865" s="26" t="s">
+        <v>9092</v>
+      </c>
+      <c r="C865" s="21" t="s">
         <v>9093</v>
-      </c>
-      <c r="C865" s="21" t="s">
-        <v>9094</v>
       </c>
     </row>
     <row r="866" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B866" s="26" t="s">
+        <v>9094</v>
+      </c>
+      <c r="C866" s="21" t="s">
         <v>9095</v>
-      </c>
-      <c r="C866" s="21" t="s">
-        <v>9096</v>
       </c>
     </row>
     <row r="867" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B867" s="26" t="s">
+        <v>9096</v>
+      </c>
+      <c r="C867" s="21" t="s">
         <v>9097</v>
-      </c>
-      <c r="C867" s="21" t="s">
-        <v>9098</v>
       </c>
     </row>
     <row r="868" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B868" s="26" t="s">
+        <v>9098</v>
+      </c>
+      <c r="C868" s="21" t="s">
         <v>9099</v>
-      </c>
-      <c r="C868" s="21" t="s">
-        <v>9100</v>
       </c>
     </row>
     <row r="869" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B869" s="26" t="s">
+        <v>9100</v>
+      </c>
+      <c r="C869" s="21" t="s">
         <v>9101</v>
-      </c>
-      <c r="C869" s="21" t="s">
-        <v>9102</v>
       </c>
     </row>
     <row r="870" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B870" s="26" t="s">
+        <v>9102</v>
+      </c>
+      <c r="C870" s="21" t="s">
         <v>9103</v>
-      </c>
-      <c r="C870" s="21" t="s">
-        <v>9104</v>
       </c>
     </row>
     <row r="871" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B871" s="26" t="s">
+        <v>9104</v>
+      </c>
+      <c r="C871" s="21" t="s">
         <v>9105</v>
-      </c>
-      <c r="C871" s="21" t="s">
-        <v>9106</v>
       </c>
     </row>
     <row r="872" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B872" s="26" t="s">
+        <v>9106</v>
+      </c>
+      <c r="C872" s="21" t="s">
         <v>9107</v>
-      </c>
-      <c r="C872" s="21" t="s">
-        <v>9108</v>
       </c>
     </row>
     <row r="873" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B873" s="26" t="s">
+        <v>9108</v>
+      </c>
+      <c r="C873" s="21" t="s">
         <v>9109</v>
-      </c>
-      <c r="C873" s="21" t="s">
-        <v>9110</v>
       </c>
     </row>
     <row r="874" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B874" s="26" t="s">
+        <v>9110</v>
+      </c>
+      <c r="C874" s="21" t="s">
         <v>9111</v>
-      </c>
-      <c r="C874" s="21" t="s">
-        <v>9112</v>
       </c>
     </row>
     <row r="875" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B875" s="26" t="s">
+        <v>9112</v>
+      </c>
+      <c r="C875" s="21" t="s">
         <v>9113</v>
-      </c>
-      <c r="C875" s="21" t="s">
-        <v>9114</v>
       </c>
     </row>
     <row r="876" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B876" s="26" t="s">
+        <v>9114</v>
+      </c>
+      <c r="C876" s="21" t="s">
         <v>9115</v>
-      </c>
-      <c r="C876" s="21" t="s">
-        <v>9116</v>
       </c>
     </row>
     <row r="877" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B877" s="26" t="s">
+        <v>9116</v>
+      </c>
+      <c r="C877" s="21" t="s">
         <v>9117</v>
-      </c>
-      <c r="C877" s="21" t="s">
-        <v>9118</v>
       </c>
     </row>
     <row r="878" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B878" s="26" t="s">
+        <v>9118</v>
+      </c>
+      <c r="C878" s="21" t="s">
         <v>9119</v>
-      </c>
-      <c r="C878" s="21" t="s">
-        <v>9120</v>
       </c>
     </row>
     <row r="879" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B879" s="26" t="s">
+        <v>9120</v>
+      </c>
+      <c r="C879" s="21" t="s">
         <v>9121</v>
-      </c>
-      <c r="C879" s="21" t="s">
-        <v>9122</v>
       </c>
     </row>
     <row r="880" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B880" s="26" t="s">
+        <v>9122</v>
+      </c>
+      <c r="C880" s="21" t="s">
         <v>9123</v>
-      </c>
-      <c r="C880" s="21" t="s">
-        <v>9124</v>
       </c>
     </row>
     <row r="881" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B881" s="26" t="s">
+        <v>9124</v>
+      </c>
+      <c r="C881" s="21" t="s">
         <v>9125</v>
-      </c>
-      <c r="C881" s="21" t="s">
-        <v>9126</v>
       </c>
     </row>
     <row r="882" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B882" s="26" t="s">
+        <v>9126</v>
+      </c>
+      <c r="C882" s="21" t="s">
         <v>9127</v>
-      </c>
-      <c r="C882" s="21" t="s">
-        <v>9128</v>
       </c>
     </row>
     <row r="883" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B883" s="26" t="s">
-        <v>9129</v>
+        <v>9128</v>
       </c>
       <c r="C883" s="21" t="s">
         <v>8301</v>
@@ -74222,21 +74375,21 @@
     </row>
     <row r="884" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B884" s="26" t="s">
+        <v>9129</v>
+      </c>
+      <c r="C884" s="21" t="s">
         <v>9130</v>
-      </c>
-      <c r="C884" s="21" t="s">
-        <v>9131</v>
       </c>
     </row>
     <row r="885" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B885" s="26" t="s">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="C885" s="21" t="s">
         <v>7762</v>
@@ -74244,1979 +74397,1979 @@
     </row>
     <row r="886" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B886" s="26" t="s">
+        <v>9132</v>
+      </c>
+      <c r="C886" s="21" t="s">
         <v>9133</v>
-      </c>
-      <c r="C886" s="21" t="s">
-        <v>9134</v>
       </c>
     </row>
     <row r="887" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B887" s="26" t="s">
+        <v>9134</v>
+      </c>
+      <c r="C887" s="21" t="s">
         <v>9135</v>
-      </c>
-      <c r="C887" s="21" t="s">
-        <v>9136</v>
       </c>
     </row>
     <row r="888" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B888" s="26" t="s">
+        <v>9136</v>
+      </c>
+      <c r="C888" s="21" t="s">
         <v>9137</v>
-      </c>
-      <c r="C888" s="21" t="s">
-        <v>9138</v>
       </c>
     </row>
     <row r="889" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B889" s="26" t="s">
+        <v>9138</v>
+      </c>
+      <c r="C889" s="21" t="s">
         <v>9139</v>
-      </c>
-      <c r="C889" s="21" t="s">
-        <v>9140</v>
       </c>
     </row>
     <row r="890" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B890" s="26" t="s">
+        <v>9140</v>
+      </c>
+      <c r="C890" s="21" t="s">
         <v>9141</v>
-      </c>
-      <c r="C890" s="21" t="s">
-        <v>9142</v>
       </c>
     </row>
     <row r="891" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B891" s="26" t="s">
+        <v>9142</v>
+      </c>
+      <c r="C891" s="21" t="s">
         <v>9143</v>
-      </c>
-      <c r="C891" s="21" t="s">
-        <v>9144</v>
       </c>
     </row>
     <row r="892" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B892" s="26" t="s">
+        <v>9144</v>
+      </c>
+      <c r="C892" s="21" t="s">
         <v>9145</v>
-      </c>
-      <c r="C892" s="21" t="s">
-        <v>9146</v>
       </c>
     </row>
     <row r="893" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B893" s="26" t="s">
+        <v>9146</v>
+      </c>
+      <c r="C893" s="21" t="s">
         <v>9147</v>
-      </c>
-      <c r="C893" s="21" t="s">
-        <v>9148</v>
       </c>
     </row>
     <row r="894" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B894" s="26" t="s">
+        <v>9148</v>
+      </c>
+      <c r="C894" s="21" t="s">
         <v>9149</v>
-      </c>
-      <c r="C894" s="21" t="s">
-        <v>9150</v>
       </c>
     </row>
     <row r="895" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B895" s="26" t="s">
+        <v>9150</v>
+      </c>
+      <c r="C895" s="21" t="s">
         <v>9151</v>
-      </c>
-      <c r="C895" s="21" t="s">
-        <v>9152</v>
       </c>
     </row>
     <row r="896" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="28" t="s">
-        <v>9024</v>
+        <v>9023</v>
       </c>
       <c r="B896" s="26" t="s">
+        <v>9152</v>
+      </c>
+      <c r="C896" s="21" t="s">
         <v>9153</v>
-      </c>
-      <c r="C896" s="21" t="s">
-        <v>9154</v>
       </c>
     </row>
     <row r="897" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="28" t="s">
+        <v>9154</v>
+      </c>
+      <c r="B897" s="26" t="s">
         <v>9155</v>
       </c>
-      <c r="B897" s="26" t="s">
+      <c r="C897" s="21" t="s">
         <v>9156</v>
-      </c>
-      <c r="C897" s="21" t="s">
-        <v>9157</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B898" s="26" t="s">
+        <v>9157</v>
+      </c>
+      <c r="C898" s="21" t="s">
         <v>9158</v>
-      </c>
-      <c r="C898" s="21" t="s">
-        <v>9159</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B899" s="26" t="s">
+        <v>9159</v>
+      </c>
+      <c r="C899" s="21" t="s">
         <v>9160</v>
-      </c>
-      <c r="C899" s="21" t="s">
-        <v>9161</v>
       </c>
     </row>
     <row r="900" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B900" s="26" t="s">
+        <v>9161</v>
+      </c>
+      <c r="C900" s="21" t="s">
         <v>9162</v>
-      </c>
-      <c r="C900" s="21" t="s">
-        <v>9163</v>
       </c>
     </row>
     <row r="901" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B901" s="26" t="s">
+        <v>9163</v>
+      </c>
+      <c r="C901" s="21" t="s">
         <v>9164</v>
-      </c>
-      <c r="C901" s="21" t="s">
-        <v>9165</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B902" s="26" t="s">
+        <v>9165</v>
+      </c>
+      <c r="C902" s="21" t="s">
         <v>9166</v>
-      </c>
-      <c r="C902" s="21" t="s">
-        <v>9167</v>
       </c>
     </row>
     <row r="903" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B903" s="26" t="s">
+        <v>9167</v>
+      </c>
+      <c r="C903" s="21" t="s">
         <v>9168</v>
-      </c>
-      <c r="C903" s="21" t="s">
-        <v>9169</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B904" s="26" t="s">
+        <v>9169</v>
+      </c>
+      <c r="C904" s="21" t="s">
         <v>9170</v>
-      </c>
-      <c r="C904" s="21" t="s">
-        <v>9171</v>
       </c>
     </row>
     <row r="905" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B905" s="26" t="s">
+        <v>9171</v>
+      </c>
+      <c r="C905" s="21" t="s">
         <v>9172</v>
-      </c>
-      <c r="C905" s="21" t="s">
-        <v>9173</v>
       </c>
     </row>
     <row r="906" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B906" s="26" t="s">
+        <v>9173</v>
+      </c>
+      <c r="C906" s="21" t="s">
         <v>9174</v>
-      </c>
-      <c r="C906" s="21" t="s">
-        <v>9175</v>
       </c>
     </row>
     <row r="907" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B907" s="26" t="s">
+        <v>9175</v>
+      </c>
+      <c r="C907" s="21" t="s">
         <v>9176</v>
-      </c>
-      <c r="C907" s="21" t="s">
-        <v>9177</v>
       </c>
     </row>
     <row r="908" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B908" s="26" t="s">
+        <v>9177</v>
+      </c>
+      <c r="C908" s="21" t="s">
         <v>9178</v>
-      </c>
-      <c r="C908" s="21" t="s">
-        <v>9179</v>
       </c>
     </row>
     <row r="909" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B909" s="26" t="s">
+        <v>9179</v>
+      </c>
+      <c r="C909" s="21" t="s">
         <v>9180</v>
-      </c>
-      <c r="C909" s="21" t="s">
-        <v>9181</v>
       </c>
     </row>
     <row r="910" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B910" s="26" t="s">
+        <v>9181</v>
+      </c>
+      <c r="C910" s="21" t="s">
         <v>9182</v>
-      </c>
-      <c r="C910" s="21" t="s">
-        <v>9183</v>
       </c>
     </row>
     <row r="911" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B911" s="26" t="s">
+        <v>9183</v>
+      </c>
+      <c r="C911" s="21" t="s">
         <v>9184</v>
-      </c>
-      <c r="C911" s="21" t="s">
-        <v>9185</v>
       </c>
     </row>
     <row r="912" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B912" s="26" t="s">
+        <v>9185</v>
+      </c>
+      <c r="C912" s="21" t="s">
         <v>9186</v>
-      </c>
-      <c r="C912" s="21" t="s">
-        <v>9187</v>
       </c>
     </row>
     <row r="913" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B913" s="26" t="s">
+        <v>9187</v>
+      </c>
+      <c r="C913" s="21" t="s">
         <v>9188</v>
-      </c>
-      <c r="C913" s="21" t="s">
-        <v>9189</v>
       </c>
     </row>
     <row r="914" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B914" s="26" t="s">
+        <v>9189</v>
+      </c>
+      <c r="C914" s="21" t="s">
         <v>9190</v>
-      </c>
-      <c r="C914" s="21" t="s">
-        <v>9191</v>
       </c>
     </row>
     <row r="915" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B915" s="26" t="s">
+        <v>9191</v>
+      </c>
+      <c r="C915" s="21" t="s">
         <v>9192</v>
-      </c>
-      <c r="C915" s="21" t="s">
-        <v>9193</v>
       </c>
     </row>
     <row r="916" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B916" s="26" t="s">
+        <v>9193</v>
+      </c>
+      <c r="C916" s="21" t="s">
         <v>9194</v>
-      </c>
-      <c r="C916" s="21" t="s">
-        <v>9195</v>
       </c>
     </row>
     <row r="917" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B917" s="26" t="s">
+        <v>9195</v>
+      </c>
+      <c r="C917" s="21" t="s">
         <v>9196</v>
-      </c>
-      <c r="C917" s="21" t="s">
-        <v>9197</v>
       </c>
     </row>
     <row r="918" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B918" s="26" t="s">
+        <v>9197</v>
+      </c>
+      <c r="C918" s="21" t="s">
         <v>9198</v>
-      </c>
-      <c r="C918" s="21" t="s">
-        <v>9199</v>
       </c>
     </row>
     <row r="919" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B919" s="26" t="s">
+        <v>9199</v>
+      </c>
+      <c r="C919" s="21" t="s">
         <v>9200</v>
-      </c>
-      <c r="C919" s="21" t="s">
-        <v>9201</v>
       </c>
     </row>
     <row r="920" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B920" s="26" t="s">
+        <v>9201</v>
+      </c>
+      <c r="C920" s="21" t="s">
         <v>9202</v>
-      </c>
-      <c r="C920" s="21" t="s">
-        <v>9203</v>
       </c>
     </row>
     <row r="921" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B921" s="26" t="s">
+        <v>9203</v>
+      </c>
+      <c r="C921" s="21" t="s">
         <v>9204</v>
-      </c>
-      <c r="C921" s="21" t="s">
-        <v>9205</v>
       </c>
     </row>
     <row r="922" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B922" s="26" t="s">
+        <v>9205</v>
+      </c>
+      <c r="C922" s="21" t="s">
         <v>9206</v>
-      </c>
-      <c r="C922" s="21" t="s">
-        <v>9207</v>
       </c>
     </row>
     <row r="923" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B923" s="26" t="s">
+        <v>9207</v>
+      </c>
+      <c r="C923" s="21" t="s">
         <v>9208</v>
-      </c>
-      <c r="C923" s="21" t="s">
-        <v>9209</v>
       </c>
     </row>
     <row r="924" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B924" s="26" t="s">
+        <v>9209</v>
+      </c>
+      <c r="C924" s="21" t="s">
         <v>9210</v>
-      </c>
-      <c r="C924" s="21" t="s">
-        <v>9211</v>
       </c>
     </row>
     <row r="925" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B925" s="26" t="s">
+        <v>9211</v>
+      </c>
+      <c r="C925" s="21" t="s">
         <v>9212</v>
-      </c>
-      <c r="C925" s="21" t="s">
-        <v>9213</v>
       </c>
     </row>
     <row r="926" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B926" s="26" t="s">
+        <v>9213</v>
+      </c>
+      <c r="C926" s="21" t="s">
         <v>9214</v>
-      </c>
-      <c r="C926" s="21" t="s">
-        <v>9215</v>
       </c>
     </row>
     <row r="927" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B927" s="26" t="s">
+        <v>9215</v>
+      </c>
+      <c r="C927" s="21" t="s">
         <v>9216</v>
-      </c>
-      <c r="C927" s="21" t="s">
-        <v>9217</v>
       </c>
     </row>
     <row r="928" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B928" s="26" t="s">
-        <v>9218</v>
+        <v>9217</v>
       </c>
       <c r="C928" s="21" t="s">
-        <v>9203</v>
+        <v>9202</v>
       </c>
     </row>
     <row r="929" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B929" s="26" t="s">
+        <v>9218</v>
+      </c>
+      <c r="C929" s="21" t="s">
         <v>9219</v>
-      </c>
-      <c r="C929" s="21" t="s">
-        <v>9220</v>
       </c>
     </row>
     <row r="930" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B930" s="26" t="s">
+        <v>9220</v>
+      </c>
+      <c r="C930" s="21" t="s">
         <v>9221</v>
-      </c>
-      <c r="C930" s="21" t="s">
-        <v>9222</v>
       </c>
     </row>
     <row r="931" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B931" s="26" t="s">
+        <v>9222</v>
+      </c>
+      <c r="C931" s="21" t="s">
         <v>9223</v>
-      </c>
-      <c r="C931" s="21" t="s">
-        <v>9224</v>
       </c>
     </row>
     <row r="932" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B932" s="26" t="s">
+        <v>9224</v>
+      </c>
+      <c r="C932" s="21" t="s">
         <v>9225</v>
-      </c>
-      <c r="C932" s="21" t="s">
-        <v>9226</v>
       </c>
     </row>
     <row r="933" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B933" s="26" t="s">
+        <v>9226</v>
+      </c>
+      <c r="C933" s="21" t="s">
         <v>9227</v>
-      </c>
-      <c r="C933" s="21" t="s">
-        <v>9228</v>
       </c>
     </row>
     <row r="934" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B934" s="26" t="s">
+        <v>9228</v>
+      </c>
+      <c r="C934" s="21" t="s">
         <v>9229</v>
-      </c>
-      <c r="C934" s="21" t="s">
-        <v>9230</v>
       </c>
     </row>
     <row r="935" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B935" s="26" t="s">
+        <v>9230</v>
+      </c>
+      <c r="C935" s="21" t="s">
         <v>9231</v>
-      </c>
-      <c r="C935" s="21" t="s">
-        <v>9232</v>
       </c>
     </row>
     <row r="936" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B936" s="26" t="s">
+        <v>9232</v>
+      </c>
+      <c r="C936" s="21" t="s">
         <v>9233</v>
-      </c>
-      <c r="C936" s="21" t="s">
-        <v>9234</v>
       </c>
     </row>
     <row r="937" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B937" s="26" t="s">
+        <v>9234</v>
+      </c>
+      <c r="C937" s="21" t="s">
         <v>9235</v>
-      </c>
-      <c r="C937" s="21" t="s">
-        <v>9236</v>
       </c>
     </row>
     <row r="938" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B938" s="26" t="s">
+        <v>9236</v>
+      </c>
+      <c r="C938" s="21" t="s">
         <v>9237</v>
-      </c>
-      <c r="C938" s="21" t="s">
-        <v>9238</v>
       </c>
     </row>
     <row r="939" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B939" s="26" t="s">
-        <v>9239</v>
+        <v>9238</v>
       </c>
       <c r="C939" s="21" t="s">
-        <v>9236</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="940" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B940" s="26" t="s">
+        <v>9239</v>
+      </c>
+      <c r="C940" s="21" t="s">
         <v>9240</v>
-      </c>
-      <c r="C940" s="21" t="s">
-        <v>9241</v>
       </c>
     </row>
     <row r="941" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B941" s="26" t="s">
-        <v>9242</v>
+        <v>9241</v>
       </c>
       <c r="C941" s="21" t="s">
-        <v>9236</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="942" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B942" s="26" t="s">
+        <v>9242</v>
+      </c>
+      <c r="C942" s="21" t="s">
         <v>9243</v>
-      </c>
-      <c r="C942" s="21" t="s">
-        <v>9244</v>
       </c>
     </row>
     <row r="943" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B943" s="26" t="s">
-        <v>9245</v>
+        <v>9244</v>
       </c>
       <c r="C943" s="21" t="s">
-        <v>9236</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="944" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A944" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B944" s="26" t="s">
+        <v>9245</v>
+      </c>
+      <c r="C944" s="21" t="s">
         <v>9246</v>
-      </c>
-      <c r="C944" s="21" t="s">
-        <v>9247</v>
       </c>
     </row>
     <row r="945" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B945" s="26" t="s">
+        <v>9247</v>
+      </c>
+      <c r="C945" s="21" t="s">
         <v>9248</v>
-      </c>
-      <c r="C945" s="21" t="s">
-        <v>9249</v>
       </c>
     </row>
     <row r="946" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B946" s="26" t="s">
+        <v>9249</v>
+      </c>
+      <c r="C946" s="21" t="s">
         <v>9250</v>
-      </c>
-      <c r="C946" s="21" t="s">
-        <v>9251</v>
       </c>
     </row>
     <row r="947" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B947" s="26" t="s">
+        <v>9251</v>
+      </c>
+      <c r="C947" s="21" t="s">
         <v>9252</v>
-      </c>
-      <c r="C947" s="21" t="s">
-        <v>9253</v>
       </c>
     </row>
     <row r="948" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B948" s="26" t="s">
+        <v>9253</v>
+      </c>
+      <c r="C948" s="21" t="s">
         <v>9254</v>
-      </c>
-      <c r="C948" s="21" t="s">
-        <v>9255</v>
       </c>
     </row>
     <row r="949" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B949" s="26" t="s">
+        <v>9255</v>
+      </c>
+      <c r="C949" s="21" t="s">
         <v>9256</v>
-      </c>
-      <c r="C949" s="21" t="s">
-        <v>9257</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B950" s="26" t="s">
+        <v>9257</v>
+      </c>
+      <c r="C950" s="21" t="s">
         <v>9258</v>
-      </c>
-      <c r="C950" s="21" t="s">
-        <v>9259</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B951" s="26" t="s">
+        <v>9259</v>
+      </c>
+      <c r="C951" s="21" t="s">
         <v>9260</v>
-      </c>
-      <c r="C951" s="21" t="s">
-        <v>9261</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B952" s="26" t="s">
+        <v>9261</v>
+      </c>
+      <c r="C952" s="21" t="s">
         <v>9262</v>
-      </c>
-      <c r="C952" s="21" t="s">
-        <v>9263</v>
       </c>
     </row>
     <row r="953" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B953" s="26" t="s">
+        <v>9263</v>
+      </c>
+      <c r="C953" s="21" t="s">
         <v>9264</v>
-      </c>
-      <c r="C953" s="21" t="s">
-        <v>9265</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B954" s="26" t="s">
+        <v>9265</v>
+      </c>
+      <c r="C954" s="21" t="s">
         <v>9266</v>
-      </c>
-      <c r="C954" s="21" t="s">
-        <v>9267</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B955" s="26" t="s">
+        <v>9267</v>
+      </c>
+      <c r="C955" s="21" t="s">
         <v>9268</v>
-      </c>
-      <c r="C955" s="21" t="s">
-        <v>9269</v>
       </c>
     </row>
     <row r="956" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B956" s="26" t="s">
+        <v>9269</v>
+      </c>
+      <c r="C956" s="21" t="s">
         <v>9270</v>
-      </c>
-      <c r="C956" s="21" t="s">
-        <v>9271</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B957" s="26" t="s">
+        <v>9271</v>
+      </c>
+      <c r="C957" s="21" t="s">
         <v>9272</v>
-      </c>
-      <c r="C957" s="21" t="s">
-        <v>9273</v>
       </c>
     </row>
     <row r="958" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B958" s="26" t="s">
+        <v>9273</v>
+      </c>
+      <c r="C958" s="21" t="s">
         <v>9274</v>
-      </c>
-      <c r="C958" s="21" t="s">
-        <v>9275</v>
       </c>
     </row>
     <row r="959" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B959" s="26" t="s">
-        <v>9276</v>
+        <v>9275</v>
       </c>
       <c r="C959" s="21" t="s">
-        <v>9215</v>
+        <v>9214</v>
       </c>
     </row>
     <row r="960" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B960" s="26" t="s">
+        <v>9276</v>
+      </c>
+      <c r="C960" s="21" t="s">
         <v>9277</v>
-      </c>
-      <c r="C960" s="21" t="s">
-        <v>9278</v>
       </c>
     </row>
     <row r="961" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B961" s="26" t="s">
+        <v>9278</v>
+      </c>
+      <c r="C961" s="21" t="s">
         <v>9279</v>
-      </c>
-      <c r="C961" s="21" t="s">
-        <v>9280</v>
       </c>
     </row>
     <row r="962" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B962" s="26" t="s">
+        <v>9280</v>
+      </c>
+      <c r="C962" s="21" t="s">
         <v>9281</v>
-      </c>
-      <c r="C962" s="21" t="s">
-        <v>9282</v>
       </c>
     </row>
     <row r="963" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B963" s="26" t="s">
+        <v>9282</v>
+      </c>
+      <c r="C963" s="21" t="s">
         <v>9283</v>
-      </c>
-      <c r="C963" s="21" t="s">
-        <v>9284</v>
       </c>
     </row>
     <row r="964" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B964" s="26" t="s">
+        <v>9284</v>
+      </c>
+      <c r="C964" s="21" t="s">
         <v>9285</v>
-      </c>
-      <c r="C964" s="21" t="s">
-        <v>9286</v>
       </c>
     </row>
     <row r="965" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B965" s="26" t="s">
+        <v>9286</v>
+      </c>
+      <c r="C965" s="21" t="s">
         <v>9287</v>
-      </c>
-      <c r="C965" s="21" t="s">
-        <v>9288</v>
       </c>
     </row>
     <row r="966" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B966" s="26" t="s">
+        <v>9288</v>
+      </c>
+      <c r="C966" s="21" t="s">
         <v>9289</v>
-      </c>
-      <c r="C966" s="21" t="s">
-        <v>9290</v>
       </c>
     </row>
     <row r="967" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B967" s="26" t="s">
+        <v>9290</v>
+      </c>
+      <c r="C967" s="21" t="s">
         <v>9291</v>
-      </c>
-      <c r="C967" s="21" t="s">
-        <v>9292</v>
       </c>
     </row>
     <row r="968" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B968" s="26" t="s">
+        <v>9292</v>
+      </c>
+      <c r="C968" s="21" t="s">
         <v>9293</v>
-      </c>
-      <c r="C968" s="21" t="s">
-        <v>9294</v>
       </c>
     </row>
     <row r="969" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B969" s="26" t="s">
+        <v>9294</v>
+      </c>
+      <c r="C969" s="21" t="s">
         <v>9295</v>
-      </c>
-      <c r="C969" s="21" t="s">
-        <v>9296</v>
       </c>
     </row>
     <row r="970" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A970" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B970" s="26" t="s">
+        <v>9296</v>
+      </c>
+      <c r="C970" s="21" t="s">
         <v>9297</v>
-      </c>
-      <c r="C970" s="21" t="s">
-        <v>9298</v>
       </c>
     </row>
     <row r="971" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B971" s="26" t="s">
+        <v>9298</v>
+      </c>
+      <c r="C971" s="21" t="s">
         <v>9299</v>
-      </c>
-      <c r="C971" s="21" t="s">
-        <v>9300</v>
       </c>
     </row>
     <row r="972" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A972" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B972" s="26" t="s">
+        <v>9300</v>
+      </c>
+      <c r="C972" s="21" t="s">
         <v>9301</v>
-      </c>
-      <c r="C972" s="21" t="s">
-        <v>9302</v>
       </c>
     </row>
     <row r="973" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B973" s="26" t="s">
+        <v>9302</v>
+      </c>
+      <c r="C973" s="21" t="s">
         <v>9303</v>
-      </c>
-      <c r="C973" s="21" t="s">
-        <v>9304</v>
       </c>
     </row>
     <row r="974" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B974" s="26" t="s">
+        <v>9304</v>
+      </c>
+      <c r="C974" s="21" t="s">
         <v>9305</v>
-      </c>
-      <c r="C974" s="21" t="s">
-        <v>9306</v>
       </c>
     </row>
     <row r="975" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B975" s="26" t="s">
+        <v>9306</v>
+      </c>
+      <c r="C975" s="21" t="s">
         <v>9307</v>
-      </c>
-      <c r="C975" s="21" t="s">
-        <v>9308</v>
       </c>
     </row>
     <row r="976" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B976" s="26" t="s">
+        <v>9308</v>
+      </c>
+      <c r="C976" s="21" t="s">
         <v>9309</v>
-      </c>
-      <c r="C976" s="21" t="s">
-        <v>9310</v>
       </c>
     </row>
     <row r="977" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B977" s="26" t="s">
+        <v>9310</v>
+      </c>
+      <c r="C977" s="21" t="s">
         <v>9311</v>
-      </c>
-      <c r="C977" s="21" t="s">
-        <v>9312</v>
       </c>
     </row>
     <row r="978" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B978" s="26" t="s">
+        <v>9312</v>
+      </c>
+      <c r="C978" s="21" t="s">
         <v>9313</v>
-      </c>
-      <c r="C978" s="21" t="s">
-        <v>9314</v>
       </c>
     </row>
     <row r="979" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B979" s="26" t="s">
+        <v>9314</v>
+      </c>
+      <c r="C979" s="21" t="s">
         <v>9315</v>
-      </c>
-      <c r="C979" s="21" t="s">
-        <v>9316</v>
       </c>
     </row>
     <row r="980" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B980" s="26" t="s">
+        <v>9316</v>
+      </c>
+      <c r="C980" s="21" t="s">
         <v>9317</v>
-      </c>
-      <c r="C980" s="21" t="s">
-        <v>9318</v>
       </c>
     </row>
     <row r="981" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B981" s="26" t="s">
+        <v>9318</v>
+      </c>
+      <c r="C981" s="21" t="s">
         <v>9319</v>
-      </c>
-      <c r="C981" s="21" t="s">
-        <v>9320</v>
       </c>
     </row>
     <row r="982" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B982" s="26" t="s">
+        <v>9320</v>
+      </c>
+      <c r="C982" s="21" t="s">
         <v>9321</v>
-      </c>
-      <c r="C982" s="21" t="s">
-        <v>9322</v>
       </c>
     </row>
     <row r="983" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B983" s="26" t="s">
+        <v>9322</v>
+      </c>
+      <c r="C983" s="21" t="s">
         <v>9323</v>
-      </c>
-      <c r="C983" s="21" t="s">
-        <v>9324</v>
       </c>
     </row>
     <row r="984" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B984" s="26" t="s">
-        <v>9325</v>
+        <v>9324</v>
       </c>
       <c r="C984" s="21" t="s">
-        <v>9197</v>
+        <v>9196</v>
       </c>
     </row>
     <row r="985" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="28" t="s">
-        <v>9155</v>
+        <v>9154</v>
       </c>
       <c r="B985" s="26" t="s">
+        <v>9325</v>
+      </c>
+      <c r="C985" s="21" t="s">
         <v>9326</v>
-      </c>
-      <c r="C985" s="21" t="s">
-        <v>9327</v>
       </c>
     </row>
     <row r="986" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="28" t="s">
+        <v>9327</v>
+      </c>
+      <c r="B986" s="26" t="s">
         <v>9328</v>
       </c>
-      <c r="B986" s="26" t="s">
+      <c r="C986" s="21" t="s">
         <v>9329</v>
-      </c>
-      <c r="C986" s="21" t="s">
-        <v>9330</v>
       </c>
     </row>
     <row r="987" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B987" s="26" t="s">
+        <v>9330</v>
+      </c>
+      <c r="C987" s="21" t="s">
         <v>9331</v>
-      </c>
-      <c r="C987" s="21" t="s">
-        <v>9332</v>
       </c>
     </row>
     <row r="988" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B988" s="26" t="s">
+        <v>9332</v>
+      </c>
+      <c r="C988" s="21" t="s">
         <v>9333</v>
-      </c>
-      <c r="C988" s="21" t="s">
-        <v>9334</v>
       </c>
     </row>
     <row r="989" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B989" s="26" t="s">
+        <v>9334</v>
+      </c>
+      <c r="C989" s="21" t="s">
         <v>9335</v>
-      </c>
-      <c r="C989" s="21" t="s">
-        <v>9336</v>
       </c>
     </row>
     <row r="990" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B990" s="26" t="s">
+        <v>9336</v>
+      </c>
+      <c r="C990" s="21" t="s">
         <v>9337</v>
-      </c>
-      <c r="C990" s="21" t="s">
-        <v>9338</v>
       </c>
     </row>
     <row r="991" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B991" s="26" t="s">
+        <v>9338</v>
+      </c>
+      <c r="C991" s="21" t="s">
         <v>9339</v>
-      </c>
-      <c r="C991" s="21" t="s">
-        <v>9340</v>
       </c>
     </row>
     <row r="992" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B992" s="26" t="s">
+        <v>9340</v>
+      </c>
+      <c r="C992" s="21" t="s">
         <v>9341</v>
-      </c>
-      <c r="C992" s="21" t="s">
-        <v>9342</v>
       </c>
     </row>
     <row r="993" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B993" s="26" t="s">
+        <v>9342</v>
+      </c>
+      <c r="C993" s="21" t="s">
         <v>9343</v>
-      </c>
-      <c r="C993" s="21" t="s">
-        <v>9344</v>
       </c>
     </row>
     <row r="994" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B994" s="26" t="s">
+        <v>9344</v>
+      </c>
+      <c r="C994" s="21" t="s">
         <v>9345</v>
-      </c>
-      <c r="C994" s="21" t="s">
-        <v>9346</v>
       </c>
     </row>
     <row r="995" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B995" s="26" t="s">
+        <v>9346</v>
+      </c>
+      <c r="C995" s="21" t="s">
         <v>9347</v>
-      </c>
-      <c r="C995" s="21" t="s">
-        <v>9348</v>
       </c>
     </row>
     <row r="996" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B996" s="26" t="s">
-        <v>9349</v>
+        <v>9348</v>
       </c>
       <c r="C996" s="21" t="s">
-        <v>9236</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="997" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B997" s="26" t="s">
+        <v>9349</v>
+      </c>
+      <c r="C997" s="21" t="s">
         <v>9350</v>
-      </c>
-      <c r="C997" s="21" t="s">
-        <v>9351</v>
       </c>
     </row>
     <row r="998" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B998" s="26" t="s">
+        <v>9351</v>
+      </c>
+      <c r="C998" s="21" t="s">
         <v>9352</v>
-      </c>
-      <c r="C998" s="21" t="s">
-        <v>9353</v>
       </c>
     </row>
     <row r="999" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B999" s="26" t="s">
+        <v>9353</v>
+      </c>
+      <c r="C999" s="21" t="s">
         <v>9354</v>
-      </c>
-      <c r="C999" s="21" t="s">
-        <v>9355</v>
       </c>
     </row>
     <row r="1000" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1000" s="26" t="s">
+        <v>9355</v>
+      </c>
+      <c r="C1000" s="21" t="s">
         <v>9356</v>
-      </c>
-      <c r="C1000" s="21" t="s">
-        <v>9357</v>
       </c>
     </row>
     <row r="1001" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1001" s="26" t="s">
+        <v>9357</v>
+      </c>
+      <c r="C1001" s="21" t="s">
         <v>9358</v>
-      </c>
-      <c r="C1001" s="21" t="s">
-        <v>9359</v>
       </c>
     </row>
     <row r="1002" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1002" s="26" t="s">
-        <v>9360</v>
+        <v>9359</v>
       </c>
       <c r="C1002" s="21" t="s">
-        <v>9253</v>
+        <v>9252</v>
       </c>
     </row>
     <row r="1003" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1003" s="26" t="s">
+        <v>9360</v>
+      </c>
+      <c r="C1003" s="21" t="s">
         <v>9361</v>
-      </c>
-      <c r="C1003" s="21" t="s">
-        <v>9362</v>
       </c>
     </row>
     <row r="1004" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1004" s="26" t="s">
+        <v>9362</v>
+      </c>
+      <c r="C1004" s="21" t="s">
         <v>9363</v>
-      </c>
-      <c r="C1004" s="21" t="s">
-        <v>9364</v>
       </c>
     </row>
     <row r="1005" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1005" s="26" t="s">
+        <v>9364</v>
+      </c>
+      <c r="C1005" s="21" t="s">
         <v>9365</v>
-      </c>
-      <c r="C1005" s="21" t="s">
-        <v>9366</v>
       </c>
     </row>
     <row r="1006" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1006" s="26" t="s">
+        <v>9366</v>
+      </c>
+      <c r="C1006" s="21" t="s">
         <v>9367</v>
-      </c>
-      <c r="C1006" s="21" t="s">
-        <v>9368</v>
       </c>
     </row>
     <row r="1007" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1007" s="26" t="s">
+        <v>9368</v>
+      </c>
+      <c r="C1007" s="21" t="s">
         <v>9369</v>
-      </c>
-      <c r="C1007" s="21" t="s">
-        <v>9370</v>
       </c>
     </row>
     <row r="1008" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1008" s="26" t="s">
+        <v>9370</v>
+      </c>
+      <c r="C1008" s="21" t="s">
         <v>9371</v>
-      </c>
-      <c r="C1008" s="21" t="s">
-        <v>9372</v>
       </c>
     </row>
     <row r="1009" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1009" s="26" t="s">
+        <v>9372</v>
+      </c>
+      <c r="C1009" s="21" t="s">
         <v>9373</v>
-      </c>
-      <c r="C1009" s="21" t="s">
-        <v>9374</v>
       </c>
     </row>
     <row r="1010" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1010" s="26" t="s">
+        <v>9374</v>
+      </c>
+      <c r="C1010" s="21" t="s">
         <v>9375</v>
-      </c>
-      <c r="C1010" s="21" t="s">
-        <v>9376</v>
       </c>
     </row>
     <row r="1011" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1011" s="26" t="s">
+        <v>9376</v>
+      </c>
+      <c r="C1011" s="21" t="s">
         <v>9377</v>
-      </c>
-      <c r="C1011" s="21" t="s">
-        <v>9378</v>
       </c>
     </row>
     <row r="1012" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1012" s="26" t="s">
+        <v>9378</v>
+      </c>
+      <c r="C1012" s="21" t="s">
         <v>9379</v>
-      </c>
-      <c r="C1012" s="21" t="s">
-        <v>9380</v>
       </c>
     </row>
     <row r="1013" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1013" s="26" t="s">
+        <v>9380</v>
+      </c>
+      <c r="C1013" s="21" t="s">
         <v>9381</v>
-      </c>
-      <c r="C1013" s="21" t="s">
-        <v>9382</v>
       </c>
     </row>
     <row r="1014" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1014" s="26" t="s">
+        <v>9382</v>
+      </c>
+      <c r="C1014" s="21" t="s">
         <v>9383</v>
-      </c>
-      <c r="C1014" s="21" t="s">
-        <v>9384</v>
       </c>
     </row>
     <row r="1015" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1015" s="26" t="s">
+        <v>9384</v>
+      </c>
+      <c r="C1015" s="21" t="s">
         <v>9385</v>
-      </c>
-      <c r="C1015" s="21" t="s">
-        <v>9386</v>
       </c>
     </row>
     <row r="1016" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1016" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1016" s="26" t="s">
+        <v>9386</v>
+      </c>
+      <c r="C1016" s="21" t="s">
         <v>9387</v>
-      </c>
-      <c r="C1016" s="21" t="s">
-        <v>9388</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1017" s="26" t="s">
+        <v>9388</v>
+      </c>
+      <c r="C1017" s="21" t="s">
         <v>9389</v>
-      </c>
-      <c r="C1017" s="21" t="s">
-        <v>9390</v>
       </c>
     </row>
     <row r="1018" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1018" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1018" s="26" t="s">
+        <v>9390</v>
+      </c>
+      <c r="C1018" s="21" t="s">
         <v>9391</v>
-      </c>
-      <c r="C1018" s="21" t="s">
-        <v>9392</v>
       </c>
     </row>
     <row r="1019" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1019" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1019" s="26" t="s">
+        <v>9392</v>
+      </c>
+      <c r="C1019" s="21" t="s">
         <v>9393</v>
-      </c>
-      <c r="C1019" s="21" t="s">
-        <v>9394</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1020" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1020" s="26" t="s">
+        <v>9394</v>
+      </c>
+      <c r="C1020" s="21" t="s">
         <v>9395</v>
-      </c>
-      <c r="C1020" s="21" t="s">
-        <v>9396</v>
       </c>
     </row>
     <row r="1021" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1021" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1021" s="26" t="s">
+        <v>9396</v>
+      </c>
+      <c r="C1021" s="21" t="s">
         <v>9397</v>
-      </c>
-      <c r="C1021" s="21" t="s">
-        <v>9398</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1022" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1022" s="26" t="s">
+        <v>9398</v>
+      </c>
+      <c r="C1022" s="21" t="s">
         <v>9399</v>
-      </c>
-      <c r="C1022" s="21" t="s">
-        <v>9400</v>
       </c>
     </row>
     <row r="1023" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1023" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1023" s="26" t="s">
+        <v>9400</v>
+      </c>
+      <c r="C1023" s="21" t="s">
         <v>9401</v>
-      </c>
-      <c r="C1023" s="21" t="s">
-        <v>9402</v>
       </c>
     </row>
     <row r="1024" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1024" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1024" s="26" t="s">
+        <v>9402</v>
+      </c>
+      <c r="C1024" s="21" t="s">
         <v>9403</v>
-      </c>
-      <c r="C1024" s="21" t="s">
-        <v>9404</v>
       </c>
     </row>
     <row r="1025" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1025" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1025" s="26" t="s">
+        <v>9404</v>
+      </c>
+      <c r="C1025" s="21" t="s">
         <v>9405</v>
-      </c>
-      <c r="C1025" s="21" t="s">
-        <v>9406</v>
       </c>
     </row>
     <row r="1026" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1026" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1026" s="26" t="s">
+        <v>9406</v>
+      </c>
+      <c r="C1026" s="21" t="s">
         <v>9407</v>
-      </c>
-      <c r="C1026" s="21" t="s">
-        <v>9408</v>
       </c>
     </row>
     <row r="1027" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1027" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1027" s="26" t="s">
+        <v>9408</v>
+      </c>
+      <c r="C1027" s="21" t="s">
         <v>9409</v>
-      </c>
-      <c r="C1027" s="21" t="s">
-        <v>9410</v>
       </c>
     </row>
     <row r="1028" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1028" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1028" s="26" t="s">
+        <v>9410</v>
+      </c>
+      <c r="C1028" s="21" t="s">
         <v>9411</v>
-      </c>
-      <c r="C1028" s="21" t="s">
-        <v>9412</v>
       </c>
     </row>
     <row r="1029" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1029" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1029" s="26" t="s">
+        <v>9412</v>
+      </c>
+      <c r="C1029" s="21" t="s">
         <v>9413</v>
-      </c>
-      <c r="C1029" s="21" t="s">
-        <v>9414</v>
       </c>
     </row>
     <row r="1030" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1030" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1030" s="26" t="s">
+        <v>9414</v>
+      </c>
+      <c r="C1030" s="21" t="s">
         <v>9415</v>
-      </c>
-      <c r="C1030" s="21" t="s">
-        <v>9416</v>
       </c>
     </row>
     <row r="1031" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1031" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1031" s="26" t="s">
+        <v>9416</v>
+      </c>
+      <c r="C1031" s="21" t="s">
         <v>9417</v>
-      </c>
-      <c r="C1031" s="21" t="s">
-        <v>9418</v>
       </c>
     </row>
     <row r="1032" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1032" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1032" s="26" t="s">
+        <v>9418</v>
+      </c>
+      <c r="C1032" s="21" t="s">
         <v>9419</v>
-      </c>
-      <c r="C1032" s="21" t="s">
-        <v>9420</v>
       </c>
     </row>
     <row r="1033" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1033" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1033" s="26" t="s">
+        <v>9420</v>
+      </c>
+      <c r="C1033" s="21" t="s">
         <v>9421</v>
-      </c>
-      <c r="C1033" s="21" t="s">
-        <v>9422</v>
       </c>
     </row>
     <row r="1034" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1034" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1034" s="26" t="s">
+        <v>9422</v>
+      </c>
+      <c r="C1034" s="21" t="s">
         <v>9423</v>
-      </c>
-      <c r="C1034" s="21" t="s">
-        <v>9424</v>
       </c>
     </row>
     <row r="1035" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1035" s="26" t="s">
+        <v>9424</v>
+      </c>
+      <c r="C1035" s="21" t="s">
         <v>9425</v>
-      </c>
-      <c r="C1035" s="21" t="s">
-        <v>9426</v>
       </c>
     </row>
     <row r="1036" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1036" s="26" t="s">
+        <v>9426</v>
+      </c>
+      <c r="C1036" s="21" t="s">
         <v>9427</v>
-      </c>
-      <c r="C1036" s="21" t="s">
-        <v>9428</v>
       </c>
     </row>
     <row r="1037" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1037" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1037" s="26" t="s">
-        <v>9429</v>
+        <v>9428</v>
       </c>
       <c r="C1037" s="21" t="s">
-        <v>9015</v>
+        <v>9014</v>
       </c>
     </row>
     <row r="1038" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1038" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1038" s="26" t="s">
-        <v>9430</v>
+        <v>9429</v>
       </c>
       <c r="C1038" s="21" t="s">
-        <v>9017</v>
+        <v>9016</v>
       </c>
     </row>
     <row r="1039" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1039" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1039" s="26" t="s">
+        <v>9430</v>
+      </c>
+      <c r="C1039" s="21" t="s">
         <v>9431</v>
-      </c>
-      <c r="C1039" s="21" t="s">
-        <v>9432</v>
       </c>
     </row>
     <row r="1040" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1040" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1040" s="26" t="s">
+        <v>9432</v>
+      </c>
+      <c r="C1040" s="21" t="s">
         <v>9433</v>
-      </c>
-      <c r="C1040" s="21" t="s">
-        <v>9434</v>
       </c>
     </row>
     <row r="1041" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1041" s="28" t="s">
-        <v>9328</v>
+        <v>9327</v>
       </c>
       <c r="B1041" s="26" t="s">
+        <v>9434</v>
+      </c>
+      <c r="C1041" s="21" t="s">
         <v>9435</v>
-      </c>
-      <c r="C1041" s="21" t="s">
-        <v>9436</v>
       </c>
     </row>
     <row r="1042" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1042" s="28" t="s">
+        <v>9436</v>
+      </c>
+      <c r="B1042" s="26" t="s">
         <v>9437</v>
       </c>
-      <c r="B1042" s="26" t="s">
+      <c r="C1042" s="21" t="s">
         <v>9438</v>
-      </c>
-      <c r="C1042" s="21" t="s">
-        <v>9439</v>
       </c>
     </row>
     <row r="1043" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1043" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1043" s="26" t="s">
+        <v>9439</v>
+      </c>
+      <c r="C1043" s="21" t="s">
         <v>9440</v>
-      </c>
-      <c r="C1043" s="21" t="s">
-        <v>9441</v>
       </c>
     </row>
     <row r="1044" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1044" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1044" s="26" t="s">
+        <v>9441</v>
+      </c>
+      <c r="C1044" s="21" t="s">
         <v>9442</v>
-      </c>
-      <c r="C1044" s="21" t="s">
-        <v>9443</v>
       </c>
     </row>
     <row r="1045" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1045" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1045" s="26" t="s">
+        <v>9443</v>
+      </c>
+      <c r="C1045" s="21" t="s">
         <v>9444</v>
-      </c>
-      <c r="C1045" s="21" t="s">
-        <v>9445</v>
       </c>
     </row>
     <row r="1046" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1046" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1046" s="26" t="s">
+        <v>9445</v>
+      </c>
+      <c r="C1046" s="21" t="s">
         <v>9446</v>
-      </c>
-      <c r="C1046" s="21" t="s">
-        <v>9447</v>
       </c>
     </row>
     <row r="1047" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1047" s="26" t="s">
+        <v>9447</v>
+      </c>
+      <c r="C1047" s="21" t="s">
         <v>9448</v>
-      </c>
-      <c r="C1047" s="21" t="s">
-        <v>9449</v>
       </c>
     </row>
     <row r="1048" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1048" s="26" t="s">
+        <v>9449</v>
+      </c>
+      <c r="C1048" s="21" t="s">
         <v>9450</v>
-      </c>
-      <c r="C1048" s="21" t="s">
-        <v>9451</v>
       </c>
     </row>
     <row r="1049" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1049" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1049" s="26" t="s">
+        <v>9451</v>
+      </c>
+      <c r="C1049" s="21" t="s">
         <v>9452</v>
-      </c>
-      <c r="C1049" s="21" t="s">
-        <v>9453</v>
       </c>
     </row>
     <row r="1050" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1050" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1050" s="26" t="s">
+        <v>9453</v>
+      </c>
+      <c r="C1050" s="21" t="s">
         <v>9454</v>
-      </c>
-      <c r="C1050" s="21" t="s">
-        <v>9455</v>
       </c>
     </row>
     <row r="1051" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1051" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1051" s="26" t="s">
+        <v>9455</v>
+      </c>
+      <c r="C1051" s="21" t="s">
         <v>9456</v>
-      </c>
-      <c r="C1051" s="21" t="s">
-        <v>9457</v>
       </c>
     </row>
     <row r="1052" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1052" s="26" t="s">
+        <v>9457</v>
+      </c>
+      <c r="C1052" s="21" t="s">
         <v>9458</v>
-      </c>
-      <c r="C1052" s="21" t="s">
-        <v>9459</v>
       </c>
     </row>
     <row r="1053" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1053" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1053" s="26" t="s">
+        <v>9459</v>
+      </c>
+      <c r="C1053" s="21" t="s">
         <v>9460</v>
-      </c>
-      <c r="C1053" s="21" t="s">
-        <v>9461</v>
       </c>
     </row>
     <row r="1054" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1054" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1054" s="26" t="s">
+        <v>9461</v>
+      </c>
+      <c r="C1054" s="21" t="s">
         <v>9462</v>
-      </c>
-      <c r="C1054" s="21" t="s">
-        <v>9463</v>
       </c>
     </row>
     <row r="1055" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1055" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1055" s="26" t="s">
+        <v>9463</v>
+      </c>
+      <c r="C1055" s="21" t="s">
         <v>9464</v>
-      </c>
-      <c r="C1055" s="21" t="s">
-        <v>9465</v>
       </c>
     </row>
     <row r="1056" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1056" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1056" s="26" t="s">
+        <v>9465</v>
+      </c>
+      <c r="C1056" s="21" t="s">
         <v>9466</v>
-      </c>
-      <c r="C1056" s="21" t="s">
-        <v>9467</v>
       </c>
     </row>
     <row r="1057" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1057" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1057" s="26" t="s">
+        <v>9467</v>
+      </c>
+      <c r="C1057" s="21" t="s">
         <v>9468</v>
-      </c>
-      <c r="C1057" s="21" t="s">
-        <v>9469</v>
       </c>
     </row>
     <row r="1058" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1058" s="26" t="s">
+        <v>9469</v>
+      </c>
+      <c r="C1058" s="21" t="s">
         <v>9470</v>
-      </c>
-      <c r="C1058" s="21" t="s">
-        <v>9471</v>
       </c>
     </row>
     <row r="1059" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1059" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1059" s="26" t="s">
+        <v>9471</v>
+      </c>
+      <c r="C1059" s="21" t="s">
         <v>9472</v>
-      </c>
-      <c r="C1059" s="21" t="s">
-        <v>9473</v>
       </c>
     </row>
     <row r="1060" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1060" s="26" t="s">
+        <v>9473</v>
+      </c>
+      <c r="C1060" s="21" t="s">
         <v>9474</v>
-      </c>
-      <c r="C1060" s="21" t="s">
-        <v>9475</v>
       </c>
     </row>
     <row r="1061" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1061" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1061" s="26" t="s">
+        <v>9475</v>
+      </c>
+      <c r="C1061" s="21" t="s">
         <v>9476</v>
-      </c>
-      <c r="C1061" s="21" t="s">
-        <v>9477</v>
       </c>
     </row>
     <row r="1062" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1062" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1062" s="26" t="s">
+        <v>9477</v>
+      </c>
+      <c r="C1062" s="21" t="s">
         <v>9478</v>
-      </c>
-      <c r="C1062" s="21" t="s">
-        <v>9479</v>
       </c>
     </row>
     <row r="1063" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1063" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1063" s="26" t="s">
+        <v>9479</v>
+      </c>
+      <c r="C1063" s="21" t="s">
         <v>9480</v>
-      </c>
-      <c r="C1063" s="21" t="s">
-        <v>9481</v>
       </c>
     </row>
     <row r="1064" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1064" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1064" s="26" t="s">
+        <v>9481</v>
+      </c>
+      <c r="C1064" s="21" t="s">
         <v>9482</v>
-      </c>
-      <c r="C1064" s="21" t="s">
-        <v>9483</v>
       </c>
     </row>
     <row r="1065" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1065" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1065" s="26" t="s">
-        <v>9484</v>
+        <v>9483</v>
       </c>
       <c r="C1065" s="21" t="s">
         <v>8676</v>
@@ -76224,43 +76377,43 @@
     </row>
     <row r="1066" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1066" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1066" s="26" t="s">
+        <v>9484</v>
+      </c>
+      <c r="C1066" s="21" t="s">
         <v>9485</v>
-      </c>
-      <c r="C1066" s="21" t="s">
-        <v>9486</v>
       </c>
     </row>
     <row r="1067" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1067" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1067" s="26" t="s">
+        <v>9486</v>
+      </c>
+      <c r="C1067" s="21" t="s">
         <v>9487</v>
-      </c>
-      <c r="C1067" s="21" t="s">
-        <v>9488</v>
       </c>
     </row>
     <row r="1068" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1068" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1068" s="26" t="s">
+        <v>9488</v>
+      </c>
+      <c r="C1068" s="21" t="s">
         <v>9489</v>
-      </c>
-      <c r="C1068" s="21" t="s">
-        <v>9490</v>
       </c>
     </row>
     <row r="1069" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1069" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1069" s="26" t="s">
-        <v>9491</v>
+        <v>9490</v>
       </c>
       <c r="C1069" s="21" t="s">
         <v>7895</v>
@@ -76268,186 +76421,186 @@
     </row>
     <row r="1070" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1070" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1070" s="26" t="s">
+        <v>9491</v>
+      </c>
+      <c r="C1070" s="21" t="s">
         <v>9492</v>
-      </c>
-      <c r="C1070" s="21" t="s">
-        <v>9493</v>
       </c>
     </row>
     <row r="1071" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1071" s="26" t="s">
+        <v>9493</v>
+      </c>
+      <c r="C1071" s="21" t="s">
         <v>9494</v>
-      </c>
-      <c r="C1071" s="21" t="s">
-        <v>9495</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1072" s="26" t="s">
+        <v>9495</v>
+      </c>
+      <c r="C1072" s="21" t="s">
         <v>9496</v>
-      </c>
-      <c r="C1072" s="21" t="s">
-        <v>9497</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1073" s="26" t="s">
+        <v>9497</v>
+      </c>
+      <c r="C1073" s="21" t="s">
         <v>9498</v>
-      </c>
-      <c r="C1073" s="21" t="s">
-        <v>9499</v>
       </c>
     </row>
     <row r="1074" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1074" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1074" s="26" t="s">
+        <v>9499</v>
+      </c>
+      <c r="C1074" s="21" t="s">
         <v>9500</v>
-      </c>
-      <c r="C1074" s="21" t="s">
-        <v>9501</v>
       </c>
     </row>
     <row r="1075" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1075" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1075" s="26" t="s">
+        <v>9501</v>
+      </c>
+      <c r="C1075" s="21" t="s">
         <v>9502</v>
-      </c>
-      <c r="C1075" s="21" t="s">
-        <v>9503</v>
       </c>
     </row>
     <row r="1076" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1076" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1076" s="26" t="s">
+        <v>9503</v>
+      </c>
+      <c r="C1076" s="21" t="s">
         <v>9504</v>
-      </c>
-      <c r="C1076" s="21" t="s">
-        <v>9505</v>
       </c>
     </row>
     <row r="1077" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1077" s="26" t="s">
+        <v>9505</v>
+      </c>
+      <c r="C1077" s="21" t="s">
         <v>9506</v>
-      </c>
-      <c r="C1077" s="21" t="s">
-        <v>9507</v>
       </c>
     </row>
     <row r="1078" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1078" s="26" t="s">
+        <v>9507</v>
+      </c>
+      <c r="C1078" s="21" t="s">
         <v>9508</v>
-      </c>
-      <c r="C1078" s="21" t="s">
-        <v>9509</v>
       </c>
     </row>
     <row r="1079" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1079" s="26" t="s">
+        <v>9509</v>
+      </c>
+      <c r="C1079" s="21" t="s">
         <v>9510</v>
-      </c>
-      <c r="C1079" s="21" t="s">
-        <v>9511</v>
       </c>
     </row>
     <row r="1080" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1080" s="26" t="s">
+        <v>9511</v>
+      </c>
+      <c r="C1080" s="21" t="s">
         <v>9512</v>
-      </c>
-      <c r="C1080" s="21" t="s">
-        <v>9513</v>
       </c>
     </row>
     <row r="1081" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1081" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1081" s="26" t="s">
+        <v>9513</v>
+      </c>
+      <c r="C1081" s="21" t="s">
         <v>9514</v>
-      </c>
-      <c r="C1081" s="21" t="s">
-        <v>9515</v>
       </c>
     </row>
     <row r="1082" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1082" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1082" s="26" t="s">
+        <v>9515</v>
+      </c>
+      <c r="C1082" s="21" t="s">
         <v>9516</v>
-      </c>
-      <c r="C1082" s="21" t="s">
-        <v>9517</v>
       </c>
     </row>
     <row r="1083" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1083" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1083" s="26" t="s">
+        <v>9517</v>
+      </c>
+      <c r="C1083" s="21" t="s">
         <v>9518</v>
-      </c>
-      <c r="C1083" s="21" t="s">
-        <v>9519</v>
       </c>
     </row>
     <row r="1084" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1084" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1084" s="26" t="s">
+        <v>9519</v>
+      </c>
+      <c r="C1084" s="21" t="s">
         <v>9520</v>
-      </c>
-      <c r="C1084" s="21" t="s">
-        <v>9521</v>
       </c>
     </row>
     <row r="1085" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1085" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1085" s="26" t="s">
+        <v>9521</v>
+      </c>
+      <c r="C1085" s="21" t="s">
         <v>9522</v>
-      </c>
-      <c r="C1085" s="21" t="s">
-        <v>9523</v>
       </c>
     </row>
     <row r="1086" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1086" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1086" s="26" t="s">
-        <v>9524</v>
+        <v>9523</v>
       </c>
       <c r="C1086" s="21" t="s">
         <v>7839</v>
@@ -76455,32 +76608,32 @@
     </row>
     <row r="1087" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1087" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1087" s="26" t="s">
+        <v>9524</v>
+      </c>
+      <c r="C1087" s="21" t="s">
         <v>9525</v>
-      </c>
-      <c r="C1087" s="21" t="s">
-        <v>9526</v>
       </c>
     </row>
     <row r="1088" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1088" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1088" s="26" t="s">
+        <v>9526</v>
+      </c>
+      <c r="C1088" s="21" t="s">
         <v>9527</v>
-      </c>
-      <c r="C1088" s="21" t="s">
-        <v>9528</v>
       </c>
     </row>
     <row r="1089" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1089" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1089" s="26" t="s">
-        <v>9529</v>
+        <v>9528</v>
       </c>
       <c r="C1089" s="21" t="s">
         <v>7845</v>
@@ -76488,670 +76641,670 @@
     </row>
     <row r="1090" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1090" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1090" s="26" t="s">
+        <v>9529</v>
+      </c>
+      <c r="C1090" s="21" t="s">
         <v>9530</v>
-      </c>
-      <c r="C1090" s="21" t="s">
-        <v>9531</v>
       </c>
     </row>
     <row r="1091" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1091" s="26" t="s">
+        <v>9531</v>
+      </c>
+      <c r="C1091" s="21" t="s">
         <v>9532</v>
-      </c>
-      <c r="C1091" s="21" t="s">
-        <v>9533</v>
       </c>
     </row>
     <row r="1092" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1092" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1092" s="26" t="s">
+        <v>9533</v>
+      </c>
+      <c r="C1092" s="21" t="s">
         <v>9534</v>
-      </c>
-      <c r="C1092" s="21" t="s">
-        <v>9535</v>
       </c>
     </row>
     <row r="1093" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1093" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1093" s="26" t="s">
+        <v>9535</v>
+      </c>
+      <c r="C1093" s="21" t="s">
         <v>9536</v>
-      </c>
-      <c r="C1093" s="21" t="s">
-        <v>9537</v>
       </c>
     </row>
     <row r="1094" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1094" s="26" t="s">
+        <v>9537</v>
+      </c>
+      <c r="C1094" s="21" t="s">
         <v>9538</v>
-      </c>
-      <c r="C1094" s="21" t="s">
-        <v>9539</v>
       </c>
     </row>
     <row r="1095" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1095" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1095" s="26" t="s">
+        <v>9539</v>
+      </c>
+      <c r="C1095" s="21" t="s">
         <v>9540</v>
-      </c>
-      <c r="C1095" s="21" t="s">
-        <v>9541</v>
       </c>
     </row>
     <row r="1096" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1096" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1096" s="26" t="s">
+        <v>9541</v>
+      </c>
+      <c r="C1096" s="21" t="s">
         <v>9542</v>
-      </c>
-      <c r="C1096" s="21" t="s">
-        <v>9543</v>
       </c>
     </row>
     <row r="1097" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1097" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1097" s="26" t="s">
+        <v>9543</v>
+      </c>
+      <c r="C1097" s="21" t="s">
         <v>9544</v>
-      </c>
-      <c r="C1097" s="21" t="s">
-        <v>9545</v>
       </c>
     </row>
     <row r="1098" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1098" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1098" s="26" t="s">
+        <v>9545</v>
+      </c>
+      <c r="C1098" s="21" t="s">
         <v>9546</v>
-      </c>
-      <c r="C1098" s="21" t="s">
-        <v>9547</v>
       </c>
     </row>
     <row r="1099" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1099" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1099" s="26" t="s">
-        <v>9548</v>
+        <v>9547</v>
       </c>
       <c r="C1099" s="21" t="s">
-        <v>9249</v>
+        <v>9248</v>
       </c>
     </row>
     <row r="1100" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1100" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1100" s="26" t="s">
+        <v>9548</v>
+      </c>
+      <c r="C1100" s="21" t="s">
         <v>9549</v>
-      </c>
-      <c r="C1100" s="21" t="s">
-        <v>9550</v>
       </c>
     </row>
     <row r="1101" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1101" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1101" s="26" t="s">
+        <v>9550</v>
+      </c>
+      <c r="C1101" s="21" t="s">
         <v>9551</v>
-      </c>
-      <c r="C1101" s="21" t="s">
-        <v>9552</v>
       </c>
     </row>
     <row r="1102" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1102" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1102" s="26" t="s">
+        <v>9552</v>
+      </c>
+      <c r="C1102" s="21" t="s">
         <v>9553</v>
-      </c>
-      <c r="C1102" s="21" t="s">
-        <v>9554</v>
       </c>
     </row>
     <row r="1103" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1103" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1103" s="26" t="s">
+        <v>9554</v>
+      </c>
+      <c r="C1103" s="21" t="s">
         <v>9555</v>
-      </c>
-      <c r="C1103" s="21" t="s">
-        <v>9556</v>
       </c>
     </row>
     <row r="1104" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1104" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1104" s="26" t="s">
+        <v>9556</v>
+      </c>
+      <c r="C1104" s="21" t="s">
         <v>9557</v>
-      </c>
-      <c r="C1104" s="21" t="s">
-        <v>9558</v>
       </c>
     </row>
     <row r="1105" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1105" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1105" s="26" t="s">
+        <v>9558</v>
+      </c>
+      <c r="C1105" s="21" t="s">
         <v>9559</v>
-      </c>
-      <c r="C1105" s="21" t="s">
-        <v>9560</v>
       </c>
     </row>
     <row r="1106" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1106" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1106" s="26" t="s">
+        <v>9560</v>
+      </c>
+      <c r="C1106" s="21" t="s">
         <v>9561</v>
-      </c>
-      <c r="C1106" s="21" t="s">
-        <v>9562</v>
       </c>
     </row>
     <row r="1107" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1107" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1107" s="26" t="s">
+        <v>9562</v>
+      </c>
+      <c r="C1107" s="21" t="s">
         <v>9563</v>
-      </c>
-      <c r="C1107" s="21" t="s">
-        <v>9564</v>
       </c>
     </row>
     <row r="1108" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1108" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1108" s="26" t="s">
+        <v>9564</v>
+      </c>
+      <c r="C1108" s="21" t="s">
         <v>9565</v>
-      </c>
-      <c r="C1108" s="21" t="s">
-        <v>9566</v>
       </c>
     </row>
     <row r="1109" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1109" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1109" s="26" t="s">
+        <v>9566</v>
+      </c>
+      <c r="C1109" s="21" t="s">
         <v>9567</v>
-      </c>
-      <c r="C1109" s="21" t="s">
-        <v>9568</v>
       </c>
     </row>
     <row r="1110" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1110" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1110" s="26" t="s">
+        <v>9568</v>
+      </c>
+      <c r="C1110" s="21" t="s">
         <v>9569</v>
-      </c>
-      <c r="C1110" s="21" t="s">
-        <v>9570</v>
       </c>
     </row>
     <row r="1111" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1111" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1111" s="26" t="s">
+        <v>9570</v>
+      </c>
+      <c r="C1111" s="21" t="s">
         <v>9571</v>
-      </c>
-      <c r="C1111" s="21" t="s">
-        <v>9572</v>
       </c>
     </row>
     <row r="1112" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1112" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1112" s="26" t="s">
+        <v>9572</v>
+      </c>
+      <c r="C1112" s="21" t="s">
         <v>9573</v>
-      </c>
-      <c r="C1112" s="21" t="s">
-        <v>9574</v>
       </c>
     </row>
     <row r="1113" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1113" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1113" s="26" t="s">
+        <v>9574</v>
+      </c>
+      <c r="C1113" s="21" t="s">
         <v>9575</v>
-      </c>
-      <c r="C1113" s="21" t="s">
-        <v>9576</v>
       </c>
     </row>
     <row r="1114" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1114" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1114" s="26" t="s">
+        <v>9576</v>
+      </c>
+      <c r="C1114" s="21" t="s">
         <v>9577</v>
-      </c>
-      <c r="C1114" s="21" t="s">
-        <v>9578</v>
       </c>
     </row>
     <row r="1115" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1115" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1115" s="26" t="s">
+        <v>9578</v>
+      </c>
+      <c r="C1115" s="21" t="s">
         <v>9579</v>
-      </c>
-      <c r="C1115" s="21" t="s">
-        <v>9580</v>
       </c>
     </row>
     <row r="1116" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1116" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1116" s="26" t="s">
+        <v>9580</v>
+      </c>
+      <c r="C1116" s="21" t="s">
         <v>9581</v>
-      </c>
-      <c r="C1116" s="21" t="s">
-        <v>9582</v>
       </c>
     </row>
     <row r="1117" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1117" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1117" s="26" t="s">
+        <v>9582</v>
+      </c>
+      <c r="C1117" s="21" t="s">
         <v>9583</v>
-      </c>
-      <c r="C1117" s="21" t="s">
-        <v>9584</v>
       </c>
     </row>
     <row r="1118" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1118" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1118" s="26" t="s">
+        <v>9584</v>
+      </c>
+      <c r="C1118" s="21" t="s">
         <v>9585</v>
-      </c>
-      <c r="C1118" s="21" t="s">
-        <v>9586</v>
       </c>
     </row>
     <row r="1119" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1119" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1119" s="26" t="s">
+        <v>9586</v>
+      </c>
+      <c r="C1119" s="21" t="s">
         <v>9587</v>
-      </c>
-      <c r="C1119" s="21" t="s">
-        <v>9588</v>
       </c>
     </row>
     <row r="1120" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1120" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1120" s="26" t="s">
+        <v>9588</v>
+      </c>
+      <c r="C1120" s="21" t="s">
         <v>9589</v>
-      </c>
-      <c r="C1120" s="21" t="s">
-        <v>9590</v>
       </c>
     </row>
     <row r="1121" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1121" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1121" s="26" t="s">
+        <v>9590</v>
+      </c>
+      <c r="C1121" s="21" t="s">
         <v>9591</v>
-      </c>
-      <c r="C1121" s="21" t="s">
-        <v>9592</v>
       </c>
     </row>
     <row r="1122" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1122" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1122" s="26" t="s">
+        <v>9592</v>
+      </c>
+      <c r="C1122" s="21" t="s">
         <v>9593</v>
-      </c>
-      <c r="C1122" s="21" t="s">
-        <v>9594</v>
       </c>
     </row>
     <row r="1123" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1123" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1123" s="26" t="s">
+        <v>9594</v>
+      </c>
+      <c r="C1123" s="21" t="s">
         <v>9595</v>
-      </c>
-      <c r="C1123" s="21" t="s">
-        <v>9596</v>
       </c>
     </row>
     <row r="1124" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1124" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1124" s="26" t="s">
+        <v>9596</v>
+      </c>
+      <c r="C1124" s="21" t="s">
         <v>9597</v>
-      </c>
-      <c r="C1124" s="21" t="s">
-        <v>9598</v>
       </c>
     </row>
     <row r="1125" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1125" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1125" s="26" t="s">
+        <v>9598</v>
+      </c>
+      <c r="C1125" s="21" t="s">
         <v>9599</v>
-      </c>
-      <c r="C1125" s="21" t="s">
-        <v>9600</v>
       </c>
     </row>
     <row r="1126" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1126" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1126" s="26" t="s">
+        <v>9600</v>
+      </c>
+      <c r="C1126" s="21" t="s">
         <v>9601</v>
-      </c>
-      <c r="C1126" s="21" t="s">
-        <v>9602</v>
       </c>
     </row>
     <row r="1127" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1127" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1127" s="26" t="s">
+        <v>9602</v>
+      </c>
+      <c r="C1127" s="21" t="s">
         <v>9603</v>
-      </c>
-      <c r="C1127" s="21" t="s">
-        <v>9604</v>
       </c>
     </row>
     <row r="1128" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1128" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1128" s="26" t="s">
+        <v>9604</v>
+      </c>
+      <c r="C1128" s="21" t="s">
         <v>9605</v>
-      </c>
-      <c r="C1128" s="21" t="s">
-        <v>9606</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1129" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1129" s="26" t="s">
+        <v>9606</v>
+      </c>
+      <c r="C1129" s="21" t="s">
         <v>9607</v>
-      </c>
-      <c r="C1129" s="21" t="s">
-        <v>9608</v>
       </c>
     </row>
     <row r="1130" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1130" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1130" s="26" t="s">
+        <v>9608</v>
+      </c>
+      <c r="C1130" s="21" t="s">
         <v>9609</v>
-      </c>
-      <c r="C1130" s="21" t="s">
-        <v>9610</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1131" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1131" s="26" t="s">
+        <v>9610</v>
+      </c>
+      <c r="C1131" s="21" t="s">
         <v>9611</v>
-      </c>
-      <c r="C1131" s="21" t="s">
-        <v>9612</v>
       </c>
     </row>
     <row r="1132" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1132" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1132" s="26" t="s">
+        <v>9612</v>
+      </c>
+      <c r="C1132" s="21" t="s">
         <v>9613</v>
-      </c>
-      <c r="C1132" s="21" t="s">
-        <v>9614</v>
       </c>
     </row>
     <row r="1133" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1133" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1133" s="26" t="s">
+        <v>9614</v>
+      </c>
+      <c r="C1133" s="21" t="s">
         <v>9615</v>
-      </c>
-      <c r="C1133" s="21" t="s">
-        <v>9616</v>
       </c>
     </row>
     <row r="1134" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1134" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1134" s="26" t="s">
+        <v>9616</v>
+      </c>
+      <c r="C1134" s="21" t="s">
         <v>9617</v>
-      </c>
-      <c r="C1134" s="21" t="s">
-        <v>9618</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1135" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1135" s="26" t="s">
+        <v>9618</v>
+      </c>
+      <c r="C1135" s="21" t="s">
         <v>9619</v>
-      </c>
-      <c r="C1135" s="21" t="s">
-        <v>9620</v>
       </c>
     </row>
     <row r="1136" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1136" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1136" s="26" t="s">
+        <v>9620</v>
+      </c>
+      <c r="C1136" s="21" t="s">
         <v>9621</v>
-      </c>
-      <c r="C1136" s="21" t="s">
-        <v>9622</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1137" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1137" s="26" t="s">
+        <v>9622</v>
+      </c>
+      <c r="C1137" s="21" t="s">
         <v>9623</v>
-      </c>
-      <c r="C1137" s="21" t="s">
-        <v>9624</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1138" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1138" s="26" t="s">
+        <v>9624</v>
+      </c>
+      <c r="C1138" s="21" t="s">
         <v>9625</v>
-      </c>
-      <c r="C1138" s="21" t="s">
-        <v>9626</v>
       </c>
     </row>
     <row r="1139" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1139" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1139" s="26" t="s">
+        <v>9626</v>
+      </c>
+      <c r="C1139" s="21" t="s">
         <v>9627</v>
-      </c>
-      <c r="C1139" s="21" t="s">
-        <v>9628</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1140" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1140" s="26" t="s">
+        <v>9628</v>
+      </c>
+      <c r="C1140" s="21" t="s">
         <v>9629</v>
-      </c>
-      <c r="C1140" s="21" t="s">
-        <v>9630</v>
       </c>
     </row>
     <row r="1141" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1141" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1141" s="26" t="s">
+        <v>9630</v>
+      </c>
+      <c r="C1141" s="21" t="s">
         <v>9631</v>
-      </c>
-      <c r="C1141" s="21" t="s">
-        <v>9632</v>
       </c>
     </row>
     <row r="1142" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1142" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1142" s="26" t="s">
+        <v>9632</v>
+      </c>
+      <c r="C1142" s="21" t="s">
         <v>9633</v>
-      </c>
-      <c r="C1142" s="21" t="s">
-        <v>9634</v>
       </c>
     </row>
     <row r="1143" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1143" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1143" s="26" t="s">
+        <v>9634</v>
+      </c>
+      <c r="C1143" s="21" t="s">
         <v>9635</v>
-      </c>
-      <c r="C1143" s="21" t="s">
-        <v>9636</v>
       </c>
     </row>
     <row r="1144" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1144" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1144" s="26" t="s">
+        <v>9636</v>
+      </c>
+      <c r="C1144" s="21" t="s">
         <v>9637</v>
-      </c>
-      <c r="C1144" s="21" t="s">
-        <v>9638</v>
       </c>
     </row>
     <row r="1145" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1145" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1145" s="26" t="s">
+        <v>9638</v>
+      </c>
+      <c r="C1145" s="21" t="s">
         <v>9639</v>
-      </c>
-      <c r="C1145" s="21" t="s">
-        <v>9640</v>
       </c>
     </row>
     <row r="1146" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1146" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1146" s="26" t="s">
+        <v>9640</v>
+      </c>
+      <c r="C1146" s="21" t="s">
         <v>9641</v>
-      </c>
-      <c r="C1146" s="21" t="s">
-        <v>9642</v>
       </c>
     </row>
     <row r="1147" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1147" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1147" s="26" t="s">
+        <v>9642</v>
+      </c>
+      <c r="C1147" s="21" t="s">
         <v>9643</v>
-      </c>
-      <c r="C1147" s="21" t="s">
-        <v>9644</v>
       </c>
     </row>
     <row r="1148" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1148" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1148" s="26" t="s">
+        <v>9644</v>
+      </c>
+      <c r="C1148" s="21" t="s">
         <v>9645</v>
-      </c>
-      <c r="C1148" s="21" t="s">
-        <v>9646</v>
       </c>
     </row>
     <row r="1149" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1149" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1149" s="26" t="s">
+        <v>9646</v>
+      </c>
+      <c r="C1149" s="21" t="s">
         <v>9647</v>
-      </c>
-      <c r="C1149" s="21" t="s">
-        <v>9648</v>
       </c>
     </row>
     <row r="1150" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1150" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1150" s="26" t="s">
-        <v>9649</v>
+        <v>9648</v>
       </c>
       <c r="C1150" s="21" t="s">
         <v>7868</v>
@@ -77159,10 +77312,10 @@
     </row>
     <row r="1151" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1151" s="28" t="s">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="B1151" s="26" t="s">
-        <v>9650</v>
+        <v>9649</v>
       </c>
       <c r="C1151" s="21" t="s">
         <v>7401</v>
